--- a/workspaces/btc_daily_14days/ma/ma_ratio_14.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>15</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.826771653546338</v>
+        <v>-5.796742361064148</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.440142215574241</v>
+        <v>-7.403916154416706</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.502926994599456</v>
+        <v>5.497652519469618</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.036890278782501</v>
+        <v>-1.021360956274528</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.77032188591292</v>
+        <v>11.74537179444452</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.396068451901428</v>
+        <v>5.391732165292581</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-14.71688229556217</v>
+        <v>-14.65717127656702</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.18844224918108</v>
+        <v>-15.12715246537748</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.25341899122333</v>
+        <v>-15.19166172170714</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.1091597245523</v>
+        <v>-16.04447864460778</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.635453174968504</v>
+        <v>-9.5911749822301</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.918593259669038</v>
+        <v>-2.895802921857594</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.340910603390959</v>
+        <v>-3.316557139761755</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.596776219964944</v>
+        <v>3.575017946880273</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.052016225246639</v>
+        <v>4.026915097545213</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.533722212172719</v>
+        <v>11.09212629339153</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>22.78419910998984</v>
+        <v>19.37280907067588</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18.37139538114155</v>
+        <v>19.50760354321748</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.28707558509618</v>
+        <v>14.63723894622274</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.06514673204386412</v>
+        <v>1.920238160732701</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702267890813864</v>
+        <v>-2.504058894262094</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.171395083479197</v>
+        <v>-2.971066642164779</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.233934210427762</v>
+        <v>-3.032606756475893</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.023869989866988</v>
+        <v>4.804612466241089</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.375958502039332</v>
+        <v>8.945864889825629</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.412375935483801</v>
+        <v>8.982394012742553</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.55153294009461</v>
+        <v>12.91132186275286</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.36506618390227</v>
+        <v>17.48806142513811</v>
       </c>
     </row>
     <row r="8">
@@ -676,673 +676,673 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>0.2948539999098614</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.76256391373924</v>
+        <v>9.767102837788059</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.3703272624397</v>
+        <v>12.14548223466635</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.20803877608466</v>
+        <v>12.27854506549119</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>15.37780328853115</v>
+        <v>14.51625130317891</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.26711473967444</v>
+        <v>9.272654481467278</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.89145729744148</v>
+        <v>11.96349038544354</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>15.13410282000761</v>
+        <v>14.27371344856952</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.952326426882252</v>
+        <v>5.893511948905534</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.51964587082799</v>
+        <v>10.59586490472059</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.898345511086156</v>
+        <v>4.8425591511539</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.35466120818722</v>
+        <v>10.43088135840978</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.93594358197976</v>
+        <v>10.01344738132967</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.18939202980714</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.107</t>
+          <t>X ≈ -0.1069</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.198869372098592</v>
+        <v>5.193242425234587</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2588638767421045</v>
+        <v>-0.2459193433317068</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.577867145701028</v>
+        <v>-2.557986478951705</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5235301673897084</v>
+        <v>-0.5103400486692422</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.912571498939563</v>
+        <v>-4.884795022642351</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.085796895105254</v>
+        <v>3.088164516946101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.075685231521717</v>
+        <v>1.084838912007449</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.318446598525114</v>
+        <v>-1.30143035760014</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.234098124348812</v>
+        <v>-5.203735129514115</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.014728367969283</v>
+        <v>-7.975335786639377</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-10.15008799032803</v>
+        <v>-10.10345185748547</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.332619519630754</v>
+        <v>-4.305374389433112</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.755268007588043</v>
+        <v>-4.726472043704511</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.36449919562525</v>
+        <v>-8.348058976199674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.09566</t>
+          <t>X ≈ -0.09564</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>55</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.68837986160738</v>
+        <v>5.680630890046203</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.259262010632455</v>
+        <v>2.263843599846808</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.04582240926180248</v>
+        <v>0.05717629872634689</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.643271309170913</v>
+        <v>-1.626356084586064</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.917579822994355</v>
+        <v>6.906461387207564</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.885478321766243</v>
+        <v>-1.866889303040175</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.791869212188537</v>
+        <v>-3.766653457143782</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.903710390651142</v>
+        <v>-7.864713921298872</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6796212530975581</v>
+        <v>-0.6639186156701484</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.998898191712946</v>
+        <v>-6.962169632100633</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.85188034085476</v>
+        <v>-10.80200559722131</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.64301382061264</v>
+        <v>-12.58778334894003</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-16.71540787335565</v>
+        <v>-16.64646128565938</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.6448401238192</v>
+        <v>-14.60680023494094</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.08438</t>
+          <t>X ≈ -0.08435</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>83</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.300667235872623</v>
+        <v>-4.275249885790764</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.503446365184217</v>
+        <v>-3.479609388329706</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.333418879485151</v>
+        <v>3.333556735278108</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.876276780656575</v>
+        <v>5.867815656682232</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.338981509079488</v>
+        <v>5.332347415785797</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.431563058880883</v>
+        <v>4.428913672304148</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.141023626281992</v>
+        <v>3.143148381471704</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.466693093125919</v>
+        <v>1.474817905831387</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.027753545319548</v>
+        <v>5.024176049727764</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.861449684892875</v>
+        <v>-1.841317230838449</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.483579185573532</v>
+        <v>-4.454006691246576</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.449891387567277</v>
+        <v>-4.420964087762357</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.872916978143259</v>
+        <v>-4.842170270828561</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.041369878518402</v>
+        <v>-7.027391691676975</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.07311</t>
+          <t>X ≈ -0.07308</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>95</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8.559193258737153</v>
+        <v>8.540477079461553</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.896620521650469</v>
+        <v>5.88826844483728</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.343762991113877</v>
+        <v>2.346731474994122</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.42144387805596</v>
+        <v>1.427463425804113</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.278271993109811</v>
+        <v>-2.259339290954486</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.180827591779853</v>
+        <v>1.188743083209616</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.096127171926199</v>
+        <v>1.10484697510902</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6282185124166233</v>
+        <v>0.6390204127245767</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.652363379848666</v>
+        <v>-3.626531501776171</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.671487086294263</v>
+        <v>-7.630813371290607</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.713066383495772</v>
+        <v>-4.681927230157186</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.679473446166064</v>
+        <v>-4.64900963291317</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.9906443286296</v>
+        <v>-2.965629660607739</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.197174703257879</v>
+        <v>-2.740771526807443</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.06183</t>
+          <t>X ≈ -0.0618</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>107</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.895307479088054</v>
+        <v>-3.871147290532086</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.76895288064005</v>
+        <v>-1.751027865618909</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.839767802729845</v>
+        <v>-6.804458990663029</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-11.38787869650071</v>
+        <v>-11.33635740628176</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.251883467491091</v>
+        <v>-7.214808430060579</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.892068954215013</v>
+        <v>-7.851934041862833</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-6.107017236921187</v>
+        <v>-6.072732632357663</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.32250017688023</v>
+        <v>-10.27259665705999</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.38678110076063</v>
+        <v>-10.33611742947253</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.495022921191044</v>
+        <v>-7.45346333547775</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.891393983908955</v>
+        <v>-4.858631453461875</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.857894480929637</v>
+        <v>-4.825844242163413</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.46810816919961</v>
+        <v>-2.444327855057196</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.279903680952224</v>
+        <v>-1.284795137234475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.05056</t>
+          <t>X ≈ -0.05053</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>162</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.110722270827402</v>
+        <v>-3.088601024557178</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.87118182240264</v>
+        <v>-2.84873462400887</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.796395139848542</v>
+        <v>-0.7820173662211261</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.422853291185824</v>
+        <v>2.42557650829928</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.120653856153766</v>
+        <v>3.120691689395649</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.564630879466691</v>
+        <v>1.571404914280684</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8617098793262556</v>
+        <v>0.8715073161727815</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2251847980915329</v>
+        <v>-0.2102987529235207</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.425471164458735</v>
+        <v>3.427242053971057</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.573452096389175</v>
+        <v>2.579435898582474</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.130364697121927</v>
+        <v>1.142040994135485</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6922094505097078</v>
+        <v>-0.674339499135975</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.733633936820432</v>
+        <v>-1.711814871806283</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2440947325840668</v>
+        <v>-0.2521425469500542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03929</t>
+          <t>X ≈ -0.03927</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.003242241778494</v>
+        <v>-1.992654262731655</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.654479119526378</v>
+        <v>-1.643341638538338</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.559414678807613</v>
+        <v>-1.547804363792309</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.901313970400686</v>
+        <v>-2.891343825680543</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4962579402351111</v>
+        <v>-0.4830823535955773</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.180775165504997</v>
+        <v>-1.168925208240665</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.212815768162343</v>
+        <v>-4.204830151912198</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.717929877044355</v>
+        <v>-2.708354431752802</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.779954843037522</v>
+        <v>-2.770412911214599</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.650990010558232</v>
+        <v>-2.641402581198641</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.349447021050437</v>
+        <v>-3.340820070658239</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.283274966957435</v>
+        <v>-5.276909684153907</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.407236294145612</v>
+        <v>-6.686291192188889</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.682484167266807</v>
+        <v>-4.70084412208827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02801</t>
+          <t>X ≈ -0.02799</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>224</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.077990251218495</v>
+        <v>1.298199677523804</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.42687622027551</v>
+        <v>-1.204481614894021</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.375570217597641</v>
+        <v>-1.154761933508944</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.692457505752721</v>
+        <v>-1.915174631139969</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.125766844615896</v>
+        <v>-2.900031216977659</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.723692845018419</v>
+        <v>-3.494801401988269</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.468504759537304</v>
+        <v>-2.244716610462604</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.385634198108299</v>
+        <v>-3.160609813641024</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.790846107494538</v>
+        <v>-4.560905946081988</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.302769218051736</v>
+        <v>-4.07834031925637</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.9272293160757101</v>
+        <v>-0.7159672148487601</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.084721669264923</v>
+        <v>-1.128486811378259</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.183056377763059</v>
+        <v>1.384996582365005</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.08852614960095195</v>
+        <v>0.2714465183059147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01674</t>
+          <t>X ≈ -0.01673</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.186689853952309</v>
+        <v>-2.479647177179558</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.958492773012438</v>
+        <v>-2.084482237881886</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.275117046321512</v>
+        <v>-3.399529053215701</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.610486274600319</v>
+        <v>-1.429799009083318</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.150001853069604</v>
+        <v>-2.27455829918263</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.009680922562672833</v>
+        <v>-0.1354277515958984</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4026749645962511</v>
+        <v>-0.5267189885125276</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8721720527380299</v>
+        <v>-0.99298039311455</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9342083521449354</v>
+        <v>-1.054424083042377</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.480900379015537</v>
+        <v>-1.596743089102105</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7635067891147571</v>
+        <v>-0.8796337589477972</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.884309747030528</v>
+        <v>-2.999797619266715</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.690141367566966</v>
+        <v>-2.80456385719544</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.438953339550807</v>
+        <v>-2.578828206968907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.005473</t>
+          <t>X ≈ -0.005457</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.619564446336099</v>
+        <v>-3.628953506005388</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.304327198960742</v>
+        <v>-2.306433064699036</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.67496490387655</v>
+        <v>-1.797144154675536</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1932833669446552</v>
+        <v>-0.1813952878968266</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5195338690189146</v>
+        <v>0.4124458398711255</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.645499457570281</v>
+        <v>3.556605688581584</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1817677043420645</v>
+        <v>0.1928506178615521</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.07253098475271</v>
+        <v>1.086650394985831</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7866456845271088</v>
+        <v>0.7984398478454509</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3930256356539203</v>
+        <v>0.400564703434803</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.262368684391539</v>
+        <v>-1.395607902199529</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.129623135848227</v>
+        <v>-2.139657759126735</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7411714088747772</v>
+        <v>-0.7416267942583801</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.526687461130152</v>
+        <v>-2.561345689486387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.005802</t>
+          <t>X ≈ 0.005813</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.831034228138364</v>
+        <v>-0.8223863480152218</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.558131697794423</v>
+        <v>-2.695648410849103</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3951171985588218</v>
+        <v>-0.3846827541523155</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.242194961559839</v>
+        <v>-5.384640213263815</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.244734929778161</v>
+        <v>-4.243665199624878</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.973245412249206</v>
+        <v>-4.973600068694488</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.984298097628511</v>
+        <v>-1.977606317134736</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1105663304488473</v>
+        <v>0.121789850138434</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7184749826849668</v>
+        <v>-0.7097188000152812</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.334418396943896</v>
+        <v>-2.330658912375696</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.769212104239074</v>
+        <v>-1.766230349434906</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.195570721256999</v>
+        <v>-0.1894357446374215</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1030917948073409</v>
+        <v>-0.09544778047010283</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1100677354324375</v>
+        <v>-0.1267815389839342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.01707</t>
+          <t>X ≈ 0.01708</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2077240344956834</v>
+        <v>-0.1960408797551878</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.03784520968297</v>
+        <v>1.050422716919854</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.071547931657747</v>
+        <v>2.085835224116181</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.34465820712245</v>
+        <v>5.361396766677011</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.520522706336003</v>
+        <v>4.537137195398564</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.103678929765884</v>
+        <v>3.119120288699868</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.464117311183834</v>
+        <v>3.31971234554122</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1403465231922354</v>
+        <v>0.1532505175383392</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.07945752536936368</v>
+        <v>0.09228964987461552</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.665358425382777</v>
+        <v>2.678809142833458</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.033397256717357</v>
+        <v>3.047375914514248</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.209188992662135</v>
+        <v>2.222155213001379</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9300564905193553</v>
+        <v>0.9424055058197993</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.75223576368434</v>
+        <v>1.741207058625093</v>
       </c>
     </row>
     <row r="21">
@@ -1352,153 +1352,153 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.721508495648571</v>
+        <v>-3.717875989975248</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.333584558053836</v>
+        <v>1.34618836679185</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.868301692402405</v>
+        <v>-1.859451181810236</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.738048559794905</v>
+        <v>-1.728726981061143</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.978224160831985</v>
+        <v>-2.970232632279348</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.733413802063687</v>
+        <v>-3.727121310522179</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.572533484248254</v>
+        <v>-5.571181940141386</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.640958878673757</v>
+        <v>-4.634188909196602</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.707622982391769</v>
+        <v>-4.701423290630231</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.786031273741429</v>
+        <v>-0.9840489699680006</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.099069025154115</v>
+        <v>-3.095930917884161</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.36080144249609</v>
+        <v>-2.357327413416165</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.726477137265611</v>
+        <v>-1.721140238560594</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.12581176976785</v>
+        <v>-1.143291912277682</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.03961</t>
+          <t>X ≈ 0.03963</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.035288540474291</v>
+        <v>-4.076550312158979</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.087390787799784</v>
+        <v>-6.1422005311845</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-9.125431300563825</v>
+        <v>-9.20077581645851</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.673592264872575</v>
+        <v>-7.734354573388963</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.568841673777392</v>
+        <v>-5.608124534428839</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.152457004784146</v>
+        <v>-6.199639393682588</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.796662087695189</v>
+        <v>-5.852787756169427</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.449854353845964</v>
+        <v>-6.773604834380855</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.488125179394785</v>
+        <v>-4.803305619025117</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.654152027063105</v>
+        <v>-6.726910510797723</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.53092467779819</v>
+        <v>-5.59827833572453</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.932806974481366</v>
+        <v>-6.008344627813656</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.591657578036809</v>
+        <v>-4.650717703349287</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.988660702205074</v>
+        <v>-7.091648719789418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.05088</t>
+          <t>X ≈ 0.05089</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>166</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5.940296619549066</v>
+        <v>5.952818909224689</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.092963740403142</v>
+        <v>-1.080053930827091</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.90951919398762</v>
+        <v>-6.896512062570018</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.58649497704284</v>
+        <v>-8.573515834644375</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.522506553560724</v>
+        <v>-8.509395749185785</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.900159778900509</v>
+        <v>-5.887093524600033</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.355294984911026</v>
+        <v>-3.342113975615788</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.018704509647478</v>
+        <v>-4.005505770692714</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.459191140458536</v>
+        <v>-2.445786012805705</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2543059105593173</v>
+        <v>-0.2408486168490995</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3824868853404055</v>
+        <v>0.3959391740605156</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.242587002712874</v>
+        <v>-1.229030956361271</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.814363245225934</v>
+        <v>0.8039336095277818</v>
       </c>
     </row>
     <row r="24">
@@ -1511,150 +1511,150 @@
         <v>140</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.390726218888524</v>
+        <v>-3.377816409312473</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.357023496913676</v>
+        <v>-2.344016365496074</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.655341792877564</v>
+        <v>-3.6423626504791</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6223344365212071</v>
+        <v>-0.6092236321462678</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.039178213091219</v>
+        <v>-6.026135316796854</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3046594982078474</v>
+        <v>0.3177257525083235</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5517618137121048</v>
+        <v>0.5649428230073426</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.640636742501961</v>
+        <v>4.654041870154792</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.007311989612944</v>
+        <v>3.020769283323162</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.898838004101158</v>
+        <v>5.912290292821268</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4785833931561712</v>
+        <v>0.4921394395077741</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.156876154004053</v>
+        <v>2.1464465183059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.07343</t>
+          <t>X ≈ 0.07344</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>136</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6471781837585908</v>
+        <v>0.6601853151761929</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04213719871902555</v>
+        <v>0.05511634111748975</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.966872251647253</v>
+        <v>-1.953761447272313</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.271746156656597</v>
+        <v>1.284789052950963</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.187012439384361</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.455123158249918</v>
+        <v>1.468304167545156</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.07646496322649909</v>
+        <v>-0.06326622427173589</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>-0.1778909029545375</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3960493549249051</v>
+        <v>-0.3825920612146874</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.108922037714642</v>
+        <v>1.122374326434752</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.423961544416763</v>
+        <v>1.437517590768365</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.67368287669305</v>
+        <v>1.663253240994898</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.0847</t>
+          <t>X ≈ 0.08471</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>96</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.881561679790025</v>
+        <v>6.894083969465647</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.436654733492496</v>
+        <v>9.449564543068547</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.958452693562514</v>
+        <v>6.971459824980116</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.963705826169949</v>
+        <v>3.976684968568414</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.55028461109778</v>
+        <v>6.563395415472719</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5977265488134407</v>
+        <v>0.6107694451078061</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.596326164874554</v>
+        <v>2.60939241917503</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.254142766092997</v>
+        <v>5.267323775388235</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.23480954657748</v>
+        <v>6.248008285532244</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.384684361549496</v>
+        <v>5.398089489202327</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.346597703898524</v>
+        <v>9.360054997608742</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.214314194577284</v>
+        <v>5.227766483297394</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.919059583632453</v>
+        <v>7.932615629984056</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.210447582575455</v>
+        <v>9.200017946877303</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>92</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>15.98482254935527</v>
+        <v>15.99734483903089</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.28629241465179</v>
+        <v>13.29920222422784</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>16.15229327327266</v>
+        <v>16.16530040469026</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.84776379718451</v>
+        <v>10.86074293958297</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.787603451677612</v>
+        <v>3.800714256052551</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9.519827998088928</v>
+        <v>9.532870894383294</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.34813775907746</v>
+        <v>8.361204013377936</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.967910882035149</v>
+        <v>8.981091891330387</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9.993867517591845</v>
+        <v>10.00706625654661</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.96982928908573</v>
+        <v>6.983234416738561</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.504206399550753</v>
+        <v>3.517663693260971</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.8864156438527</v>
+        <v>7.899867932572811</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.37920451116873</v>
+        <v>6.392760557520333</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.281099756488381</v>
+        <v>2.270670120790228</v>
       </c>
     </row>
     <row r="28">
@@ -1719,98 +1719,98 @@
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.271267562142924</v>
+        <v>9.283789851818547</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.130282184472826</v>
+        <v>9.143191994048877</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>11.67658994846447</v>
+        <v>11.68959707988207</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>11.80684308107197</v>
+        <v>11.81982222347043</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.797833630705682</v>
+        <v>9.810944435080621</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.154099097833111</v>
+        <v>7.167141994127476</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.42230655703141</v>
+        <v>14.43537281133189</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>15.425711393544</v>
+        <v>15.43889240283924</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>18.30588797794997</v>
+        <v>18.31908671690474</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>17.45576279292209</v>
+        <v>17.46916792057492</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>12.8392447627221</v>
+        <v>12.85270205643232</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.461863214185186</v>
+        <v>8.475315502905296</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.98278507382843</v>
+        <v>10.99634112018003</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.761918170810688</v>
+        <v>9.751488535112536</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1186</t>
+          <t>X ≈ 0.1185</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>64</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.881561679790025</v>
+        <v>6.894083969465647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.105011933174275</v>
+        <v>-4.092102123598224</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.00011936022922</v>
+        <v>8.013126491646823</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.71695127776451</v>
+        <v>10.73006208213945</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.804659498207847</v>
+        <v>7.817725752508323</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.46247609942639</v>
+        <v>10.47565710872163</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.838976213244088</v>
+        <v>8.852174952198851</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.426351028216118</v>
+        <v>6.439756155868949</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.784097703898581</v>
+        <v>7.797554997608799</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.380980861244012</v>
+        <v>9.394433149964122</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.835726250299068</v>
+        <v>5.849282296650671</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.085447582575355</v>
+        <v>6.075017946877203</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>35</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7.506561679789989</v>
+        <v>7.519083969465612</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.7521309239687</v>
+        <v>8.765040733544751</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.357262217371989</v>
+        <v>8.370269348789591</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.487515349979532</v>
+        <v>8.500494492377996</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.949094134907362</v>
+        <v>7.962204939282302</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.67510750119446</v>
+        <v>19.68815039748883</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.59037378392225</v>
+        <v>19.60344003822273</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>16.26604752799789</v>
+        <v>16.27922853729313</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>19.06219049895845</v>
+        <v>19.07538923791321</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>21.06920817107331</v>
+        <v>21.08261329872614</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.86445484675581</v>
+        <v>20.87791214046602</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>18.0416951469583</v>
+        <v>18.05514743567841</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.77785372522214</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.72830472543262</v>
+        <v>20.71787508973447</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>42</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.268466441694827</v>
+        <v>2.280988731370449</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.18070235254009</v>
+        <v>10.19361216211614</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>14.54773840784819</v>
+        <v>14.56074553926579</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>19.43989630236046</v>
+        <v>19.45287544475892</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.52052270633594</v>
+        <v>16.53363351071088</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.8179646440516</v>
+        <v>16.83100754034596</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.88509514704544</v>
+        <v>13.89827615634068</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.062190498958294</v>
+        <v>9.075389237913058</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.97397007583521</v>
+        <v>12.98737520348804</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.38826437056518</v>
+        <v>10.4017216642754</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.80359990886302</v>
+        <v>12.81705219758313</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.38334529791822</v>
+        <v>12.39690134426982</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.00358937544868</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>37</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.844789671561365</v>
+        <v>-3.832267381885742</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.45636328452558</v>
+        <v>-5.443453474949528</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.445826585716766</v>
+        <v>-0.4328194542991639</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.387129249593436</v>
+        <v>2.4001083919919</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.848708034521266</v>
+        <v>1.861818838896205</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.848852674939629</v>
+        <v>4.861895571233994</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.343989150440763</v>
+        <v>-3.330922896140287</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.296935558885849</v>
+        <v>4.310116568181087</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.235935672703548</v>
+        <v>4.249134411658311</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6831077849729184</v>
+        <v>0.6965129126257494</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.883759866060743</v>
+        <v>5.89721715977096</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.918143023406216</v>
+        <v>5.931595312126326</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.497888412461272</v>
+        <v>5.511444458812875</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.044907042034858</v>
+        <v>3.034477406336705</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.106341546016381</v>
+        <v>-4.093819256340758</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.41111709908376</v>
+        <v>10.42402690865981</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3388290376485301</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.694888621868984</v>
+        <v>3.707867764267448</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.382273858409647</v>
+        <v>6.395384662784586</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.679715796125308</v>
+        <v>6.692758692419673</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16.27240143369176</v>
+        <v>16.28546768799224</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.127798680071571</v>
+        <v>6.140979689366809</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.51841169711505</v>
+        <v>12.53161043606981</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.66828651208712</v>
+        <v>11.68169163973995</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.4635331877695</v>
+        <v>11.47699048147972</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.49791634511497</v>
+        <v>11.51136863383508</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.52927463739588</v>
+        <v>17.54283068374748</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>17.77899596967212</v>
+        <v>17.76856633397397</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>24</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.17322834645672</v>
+        <v>14.18575063613235</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.105011933174197</v>
+        <v>-4.092102123598146</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.46370582617002</v>
+        <v>16.47668496856848</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.741382055568792</v>
+        <v>-0.7282712511938527</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.610606784519796</v>
+        <v>-4.59756388822543</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.337476099426354</v>
+        <v>7.350657108721592</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.289674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.221597703898667</v>
+        <v>6.235054997608884</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.58931419457737</v>
+        <v>14.60276648329748</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.16905958363247</v>
+        <v>14.18261562998407</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.41878091590875</v>
+        <v>14.4083512802106</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,55 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1464</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+          <t>X &gt; -0.1463</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3197438693621848</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1103869637141699</v>
+        <v>-0.1106658754301364</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2232432986173549</v>
+        <v>-0.2234970118958515</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2263862458580164</v>
+        <v>-0.2266385895937972</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1647724386169145</v>
+        <v>-0.1650430266359137</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.04958942086123841</v>
+        <v>-0.04988662661177301</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.07205283055922962</v>
+        <v>-0.07234516947745107</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.08545025242093374</v>
+        <v>-0.08574210849950958</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01060161348132027</v>
+        <v>-0.01091227559660268</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.0148974417960801</v>
+        <v>-0.01521202817408351</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.03893364905039221</v>
+        <v>0.03860456921222521</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01363454725920121</v>
+        <v>0.01331170040486285</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.04812213466951221</v>
+        <v>0.04778829714054922</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.04219837894883227</v>
+        <v>0.04243587926333703</v>
       </c>
     </row>
     <row r="7">
@@ -2267,52 +2265,50 @@
           <t>X &gt; -0.1351</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4066~4079</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4067</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2992730836323787</v>
+        <v>-0.2995434815147391</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08343272768134824</v>
+        <v>-0.08376674728044975</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2443005563761744</v>
+        <v>-0.2445978830466942</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2234057210985512</v>
+        <v>-0.2237074768570793</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2086622191680121</v>
+        <v>-0.2089712839056972</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.06961513012611675</v>
+        <v>-0.06995652626227411</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.01819834613289117</v>
+        <v>-0.01855308892511687</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.02991093397243105</v>
+        <v>-0.03026604374583997</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.04545189489478929</v>
+        <v>0.04507770269000844</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.04428714615227847</v>
+        <v>0.04390747004241291</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.07450996735396842</v>
+        <v>0.07412133667513388</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.0244174394151031</v>
+        <v>0.02404116176063553</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.06058486844516864</v>
+        <v>0.06019675092800014</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.0291268742625661</v>
+        <v>0.0294069313867098</v>
       </c>
     </row>
     <row r="8">
@@ -2321,106 +2317,102 @@
           <t>X &gt; -0.1238</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4044</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3120234816593239</v>
+        <v>-0.3241499472215637</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.135583925284692</v>
+        <v>-0.1473289480557796</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3691778037658935</v>
+        <v>-0.3561706723482914</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3242402353330291</v>
+        <v>-0.3359280884945051</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2818459095041845</v>
+        <v>-0.2934081867971372</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.06963936102525992</v>
+        <v>-0.08127563551075667</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.00720208028638325</v>
+        <v>-0.004416928311187007</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.002030073413116895</v>
+        <v>-0.01354042214257589</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07408055999636787</v>
+        <v>0.06258184278912182</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.02812968434263752</v>
+        <v>0.01683125468322544</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0349162114350321</v>
+        <v>0.02366384366760599</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01564543633384829</v>
+        <v>-0.02690891627413805</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.001727396178019092</v>
+        <v>-0.01289322868921516</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.05945845105467384</v>
+        <v>-0.06988808675282598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1126</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4007~4020</t>
-        </is>
+          <t>X &gt; -0.1125</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4008</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3292592157323639</v>
+        <v>-0.3297098629143633</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2358902611165021</v>
+        <v>-0.2363807305633543</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4680239946737572</v>
+        <v>-0.4684609679202723</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4487910620550366</v>
+        <v>-0.4492317395782024</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4259770090880863</v>
+        <v>-0.4264290804196733</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1647786400615416</v>
+        <v>-0.1652929718908069</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1113843483292314</v>
+        <v>-0.1119131017880193</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1413427393475928</v>
+        <v>-0.141869049723816</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.0107733219180659</v>
+        <v>0.01020821908148406</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07763800195088777</v>
+        <v>-0.07819000564646217</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.01905067515379244</v>
+        <v>-0.01961964711819775</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.120297512415263</v>
+        <v>-0.1208411642503364</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1023975021958918</v>
+        <v>-0.1029501802761956</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1629926470228114</v>
+        <v>-0.162507003222558</v>
       </c>
     </row>
     <row r="10">
@@ -2429,916 +2421,882 @@
           <t>X &gt; -0.1013</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3955~3968</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3956</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4017044492422386</v>
+        <v>-0.4023068090679871</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2355891955891494</v>
+        <v>-0.2362553494046296</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.440374840476828</v>
+        <v>-0.4409950107479688</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4478116181343239</v>
+        <v>-0.4484284958793268</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3671809119428531</v>
+        <v>-0.3678256858302902</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2073769081635319</v>
+        <v>-0.2080583382759187</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1269407037103321</v>
+        <v>-0.1276439169339696</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1259169831285263</v>
+        <v>-0.1266270911774114</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.07950651627438532</v>
+        <v>0.07874336926525416</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02637628711992335</v>
+        <v>0.02561474172757272</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1137149348232924</v>
+        <v>0.1129281979119057</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.06509571191747909</v>
+        <v>-0.06583718859069876</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.04142238468571691</v>
+        <v>-0.04217587873467465</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05551322652700463</v>
+        <v>-0.05491127455854894</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.09001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3900~3913</t>
-        </is>
+          <t>X &gt; -0.08998</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3901</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4873049187277374</v>
+        <v>-0.4880698373815662</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2706561049533747</v>
+        <v>-0.2715041169536647</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.4472086888631281</v>
+        <v>-0.4480187026272517</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4310085813321152</v>
+        <v>-0.4318209548952581</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4695734088561068</v>
+        <v>-0.4703854881930383</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1837899984399982</v>
+        <v>-0.1846705651249252</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.07542752508363293</v>
+        <v>-0.07633770706174658</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.01659456109587865</v>
+        <v>-0.0175281996991572</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.09017659736701233</v>
+        <v>0.08921412270576923</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1251215200194338</v>
+        <v>0.1241351571493965</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2678441809675007</v>
+        <v>0.2668172926907673</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1116958791835359</v>
+        <v>0.1107090915475268</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1929423487354143</v>
+        <v>0.191927094190433</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1495501466779672</v>
+        <v>0.1502550655647639</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07874</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3817~3830</t>
-        </is>
+          <t>X &gt; -0.07871</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3818</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4046654742569729</v>
+        <v>-0.4057398363291895</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2005982481389736</v>
+        <v>-0.2017626980107181</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5291387379944368</v>
+        <v>-0.5302268643208379</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5676938776885336</v>
+        <v>-0.5687695768860763</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5954507086442717</v>
+        <v>-0.5965318556708468</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2838093988989101</v>
+        <v>-0.2849658746342456</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.14513129677119</v>
+        <v>-0.1463265350733352</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.04873891496021798</v>
+        <v>-0.04997050634113265</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.0168257229149944</v>
+        <v>-0.01806765831644697</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1681725409091754</v>
+        <v>0.1668623829752178</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3708123635844487</v>
+        <v>0.3694439010372221</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.210550120212325</v>
+        <v>0.2092237258803493</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3027246787957054</v>
+        <v>0.3013639934299803</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.305384705970738</v>
+        <v>0.3062908646352369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06747</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3723~3735</t>
-        </is>
+          <t>X &gt; -0.06744</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3723</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6326618811202778</v>
+        <v>-0.6340209555878857</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.355681456473647</v>
+        <v>-0.3571623645620292</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6022112049998682</v>
+        <v>-0.6036383717704652</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6182877429618188</v>
+        <v>-0.619707566479299</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5526480253713828</v>
+        <v>-0.5541019049988165</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3210625485948952</v>
+        <v>-0.3225705888419199</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1767027973136948</v>
+        <v>-0.1782527997704477</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.06595737696846271</v>
+        <v>-0.06755152630116612</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.07564444506592594</v>
+        <v>0.07400971614734431</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3675748607443339</v>
+        <v>0.3658361129390215</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5001211938314682</v>
+        <v>0.4983400217633829</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.33492822966506</v>
+        <v>0.3331915392258651</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3864917619832298</v>
+        <v>0.3847280539009859</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3944725624303587</v>
+        <v>0.3840429267322065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05619</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3616~3628</t>
-        </is>
+          <t>X &gt; -0.05617</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3616</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5364372176741483</v>
+        <v>-0.5382320955660376</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3140000776462486</v>
+        <v>-0.3159168975783331</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.418247986709595</v>
+        <v>-0.4201516996959285</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3006619899219487</v>
+        <v>-0.302594310710802</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3550685897851551</v>
+        <v>-0.3570068833777995</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.09777211711712397</v>
+        <v>-0.09977139374423416</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.001801020842357559</v>
+        <v>-0.00383096844112174</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2365371322902377</v>
+        <v>0.2344229839286953</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3842110198739235</v>
+        <v>0.3820527483877498</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5994651481387905</v>
+        <v>0.5972147194049029</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6591322533734285</v>
+        <v>0.6568566002614631</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4880792853523914</v>
+        <v>0.485851060411882</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4706820025115022</v>
+        <v>0.4684418211185033</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.443854662221419</v>
+        <v>0.4334250265232669</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04492</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3454~3466</t>
-        </is>
+          <t>X &gt; -0.0449</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3454</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4161157581788189</v>
+        <v>-0.4186143287749005</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1944780226403253</v>
+        <v>-0.1971223197897487</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4005734804174708</v>
+        <v>-0.4031794246591431</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4279584341052853</v>
+        <v>-0.4305513670743295</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5175230145520686</v>
+        <v>-0.5201183972137216</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1754724302869448</v>
+        <v>-0.1781531429914978</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.04216131104066534</v>
+        <v>-0.04488620935237009</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2581179034159788</v>
+        <v>0.2552813861782752</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2420632577785042</v>
+        <v>0.2392268458097249</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5072014765817983</v>
+        <v>0.5042442993045029</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6371069631578337</v>
+        <v>0.6341004127086052</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5432456948185376</v>
+        <v>0.540266483297458</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5737111952904286</v>
+        <v>0.57070053109355</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4760092502071345</v>
+        <v>0.4655796145089823</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03365</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3251~3262</t>
-        </is>
+          <t>X &gt; -0.03363</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3251</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3168595341891347</v>
+        <v>-0.3203276149658549</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1031720067712953</v>
+        <v>-0.1068170224332547</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3281014986665269</v>
+        <v>-0.3317063817049544</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2732789339813593</v>
+        <v>-0.2768937635378634</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5188528965755737</v>
+        <v>-0.5224310139022776</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1126024860856845</v>
+        <v>-0.116287031258004</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.218664412212803</v>
+        <v>0.214870364114141</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.444234931991673</v>
+        <v>0.4403376984022174</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4310551929613595</v>
+        <v>0.4271557509699733</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.704709466580745</v>
+        <v>0.7006658055309387</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8864193521150625</v>
+        <v>0.8823036911224733</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9076265087370885</v>
+        <v>0.903504490677534</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.010287923630393</v>
+        <v>1.023843969981996</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7986127625200368</v>
+        <v>0.7881831268218846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02238</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3028~3038</t>
-        </is>
+          <t>X &gt; -0.02236</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3027</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4197056013159681</v>
+        <v>-0.4400997040037353</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.005571696098172652</v>
+        <v>-0.02558911734200109</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2508687820633142</v>
+        <v>-0.2707997270620481</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1686390392885357</v>
+        <v>-0.1556598968900715</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3266380432638414</v>
+        <v>-0.3464870279462531</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1536530242503673</v>
+        <v>0.1337252644286764</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4167967013741105</v>
+        <v>0.3968814253315855</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.726621595962186</v>
+        <v>0.7068101935121192</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8160801736401311</v>
+        <v>0.7962756122648571</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.07392448480249</v>
+        <v>1.054315416351002</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.020144599539272</v>
+        <v>1.000576794174187</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.054527756884703</v>
+        <v>1.053873189607337</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9975492357680693</v>
+        <v>0.9971184380448292</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8509693791407855</v>
+        <v>0.8264219772703711</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01111</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2702~2712</t>
-        </is>
+          <t>X &gt; -0.01109</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2702</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2073026269946325</v>
+        <v>-0.1947803373190098</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2291820911710261</v>
+        <v>0.2220571684372175</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1126654856904352</v>
+        <v>0.1055278195700566</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.004680355516640589</v>
+        <v>-0.002404822329438616</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1074578802857076</v>
+        <v>-0.1145761607546092</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1732868246416075</v>
+        <v>0.1660993318631583</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5153025137289546</v>
+        <v>0.507973258973081</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.9188069681879369</v>
+        <v>0.9112631693276825</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.026476213244088</v>
+        <v>1.018880127799591</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.38103101341779</v>
+        <v>1.373188108531707</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.234551071774234</v>
+        <v>1.226730913258073</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.52800158663262</v>
+        <v>1.54145387535273</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.440833578204369</v>
+        <v>1.454389624555972</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.246439440458445</v>
+        <v>1.236009804760293</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001635</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2262~2268</t>
-        </is>
+          <t>X &gt; 0.0001758</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2262</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4607063006013092</v>
+        <v>0.473228590276932</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7251601003502515</v>
+        <v>0.7138943490649652</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4626248741241881</v>
+        <v>0.4756320055417902</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.04343515832653111</v>
+        <v>0.0324120675245112</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2302022968162518</v>
+        <v>-0.2170914924413125</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.506458505614269</v>
+        <v>-0.4934156093199036</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5805976880533663</v>
+        <v>0.569270324441284</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.888712848542994</v>
+        <v>0.8771471749467921</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.07342716331037</v>
+        <v>1.061759757852563</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.574450055625533</v>
+        <v>1.56238099015976</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.723366050494512</v>
+        <v>1.73682334420473</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.244044521721463</v>
+        <v>2.257496810441573</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.867998575674889</v>
+        <v>1.881554622026492</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.985093913256208</v>
+        <v>1.974664277558055</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.01144</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1873~1877</t>
-        </is>
+          <t>X &gt; 0.01145</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1873</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7297902359967381</v>
+        <v>0.7423125256723608</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.409106340667009</v>
+        <v>1.42201615024306</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.641302098641539</v>
+        <v>0.6543092300591411</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.144490766677919</v>
+        <v>1.157469909076383</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6060695516057493</v>
+        <v>0.6191803559806885</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4240229437699909</v>
+        <v>0.4370658400643563</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.114894039785717</v>
+        <v>1.098226551655948</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.050809432759728</v>
+        <v>1.03402597865766</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.446700332774512</v>
+        <v>1.429674952198852</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.388710878723366</v>
+        <v>2.370919442955433</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.450908969248289</v>
+        <v>2.464366262958507</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.752243541436215</v>
+        <v>2.765695830156325</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.278598647522813</v>
+        <v>2.292154693874416</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.421539413862106</v>
+        <v>2.411109778163954</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02271</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1524~1527</t>
-        </is>
+          <t>X &gt; 0.02272</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1524</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9446756287094757</v>
+        <v>0.9571979183850985</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.494202212208869</v>
+        <v>1.50711202178492</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3134788887164035</v>
+        <v>0.3264860201340056</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1817804823586187</v>
+        <v>0.1947596247570829</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2911528479722278</v>
+        <v>-0.2780420435972886</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1901745644805359</v>
+        <v>-0.1771316681861705</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5764342198843835</v>
+        <v>0.5895004741848595</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.259494448050241</v>
+        <v>1.235725871000604</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.760082770621139</v>
+        <v>1.735939696628741</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.325301159449758</v>
+        <v>2.300411893573909</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.317398228832964</v>
+        <v>2.330855522543182</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.876715769380496</v>
+        <v>2.890168058100606</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.587694754236111</v>
+        <v>2.601250800587714</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.574948894911358</v>
+        <v>2.564519259213206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.03398</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1240~1242</t>
-        </is>
+          <t>X &gt; 0.03399</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1240</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.01541836255975</v>
+        <v>2.027940652235372</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.531058920287926</v>
+        <v>1.543968729863977</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8141290220649253</v>
+        <v>0.8271361534825274</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6223209630460147</v>
+        <v>0.6353001054444789</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3254456416936549</v>
+        <v>0.3385564460685941</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6228875794093156</v>
+        <v>0.635930475703681</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.987429224455873</v>
+        <v>2.000495478756349</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.61346320659802</v>
+        <v>2.580125707755442</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.24421814872796</v>
+        <v>3.210303477581604</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.039254254022616</v>
+        <v>3.052659381675447</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.560307381317934</v>
+        <v>3.573764675028151</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.078561506405308</v>
+        <v>4.092013795125418</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.577661734170078</v>
+        <v>3.591217780521681</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.42415725999475</v>
+        <v>3.413727624296598</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.04525</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1015~1015</t>
-        </is>
+          <t>X &gt; 0.04526</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1015</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.368630645307263</v>
+        <v>3.381152934982886</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.23488954465828</v>
+        <v>3.247799354234331</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.037065173037064</v>
+        <v>3.050072304454666</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.477663133230763</v>
+        <v>2.490642275629227</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.643675415695547</v>
+        <v>1.656786220070487</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.138161688386575</v>
+        <v>2.15120458468094</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.728304818404936</v>
+        <v>3.741371072705412</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.640431764451016</v>
+        <v>4.653612773746254</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.973520548219454</v>
+        <v>4.986719287174218</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.207139205556068</v>
+        <v>5.220544333208899</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.593518886164588</v>
+        <v>5.606976179874806</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.317557215923813</v>
+        <v>6.331009504643923</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.404691767540491</v>
+        <v>5.418247813892094</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.752935267304458</v>
+        <v>5.742505631606306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.05652</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>849~849</t>
-        </is>
+          <t>X &gt; 0.05653</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>849</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.865807851757047</v>
+        <v>2.87833014143267</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.081089362467701</v>
+        <v>4.093999172043752</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.981862587555447</v>
+        <v>4.99486971897305</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.640973199550459</v>
+        <v>4.653952341948923</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.631409463865808</v>
+        <v>3.644520268240747</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.45770888096898</v>
+        <v>3.470751777263345</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.610902136606001</v>
+        <v>5.623968390906477</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.203789409202599</v>
+        <v>6.216970418497837</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.731717673785901</v>
+        <v>6.744916412740665</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.706091899829829</v>
+        <v>6.71949702748266</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.736909835818494</v>
+        <v>6.750367129528712</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.478006774082644</v>
+        <v>7.491459062802754</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.704395272678376</v>
+        <v>6.717951319029979</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.718545344648433</v>
+        <v>6.708115708950281</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.06779</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>709~709</t>
-        </is>
+          <t>X &gt; 0.0678</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>709</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.62926971928227</v>
+        <v>4.641792008957893</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.55648313029544</v>
+        <v>5.569392939871491</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.431007935687575</v>
+        <v>6.444015067105177</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.279173621186459</v>
+        <v>6.292152763584923</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.471358894125579</v>
+        <v>4.484469698500519</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.332975726058443</v>
+        <v>5.346018622352808</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.658679244329193</v>
+        <v>6.671745498629669</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.319845633982105</v>
+        <v>7.333026643277343</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.681976918462709</v>
+        <v>7.695175657417472</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.113939180543383</v>
+        <v>7.127344308196214</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.473360750443014</v>
+        <v>7.486818044153232</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.789831354897046</v>
+        <v>7.803283643617156</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.933751638169348</v>
+        <v>7.94730768452095</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.619298076228432</v>
+        <v>7.60886844053028</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.07906</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>573~573</t>
-        </is>
+          <t>X &gt; 0.07907</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>573</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.621744925863325</v>
+        <v>5.634267215538948</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.755372010979343</v>
+        <v>5.768281820555394</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.803784281695151</v>
+        <v>7.816791413112753</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.759517344494611</v>
+        <v>7.772496486893075</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.99945564076625</v>
+        <v>6.012566445141189</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.296897578481911</v>
+        <v>6.309940474776276</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.957364559289914</v>
+        <v>7.97043081359039</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.711821649164612</v>
+        <v>8.72500265845985</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.523422112022452</v>
+        <v>9.536620850977215</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.84781699680255</v>
+        <v>8.861222124455381</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.341143951717072</v>
+        <v>9.35460124542729</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.375527109062503</v>
+        <v>9.388979397782613</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.478832707541692</v>
+        <v>9.492388753893295</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.030473760585863</v>
+        <v>9.020044124887711</v>
       </c>
     </row>
     <row r="27">
@@ -3347,52 +3305,50 @@
           <t>X &gt; 0.09034</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>477~477</t>
-        </is>
+      <c r="B27" t="n">
+        <v>477</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.368196899915809</v>
+        <v>5.380719189591431</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.014484922171675</v>
+        <v>5.027394731747727</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.973913909495423</v>
+        <v>7.986921040913025</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.523454253842964</v>
+        <v>8.536433396241428</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.888596980070595</v>
+        <v>5.901707784445534</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.44390055300638</v>
+        <v>7.456943449300745</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.036315682694266</v>
+        <v>9.049381936994742</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.407706707392855</v>
+        <v>9.420887716688092</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.18528124469062</v>
+        <v>10.19847998364538</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.544799665532722</v>
+        <v>9.558204793185553</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.340046341215142</v>
+        <v>9.35350363492536</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.21300392204066</v>
+        <v>10.22645621076077</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.792749311095754</v>
+        <v>9.806305357447357</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.994252614021931</v>
+        <v>8.983822978323779</v>
       </c>
     </row>
     <row r="28">
@@ -3401,52 +3357,50 @@
           <t>X &gt; 0.1016</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>385~385</t>
-        </is>
+      <c r="B28" t="n">
+        <v>385</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.831237004465343</v>
+        <v>2.843759294140966</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.019599879709695</v>
+        <v>6.032607011127297</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.968034830499015</v>
+        <v>7.981013972897479</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.390652576465804</v>
+        <v>6.403763380840743</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.947834773921727</v>
+        <v>6.960877670216092</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.200763394311785</v>
+        <v>9.213829648612261</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.512800774751064</v>
+        <v>9.525981784046301</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.23102166778954</v>
+        <v>10.2442204067443</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.16011726198239</v>
+        <v>10.17352238963522</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.73458471688559</v>
+        <v>10.74804201059581</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.76896787423102</v>
+        <v>10.78242016295113</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.60845352302638</v>
+        <v>10.62200956937798</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.59843459556241</v>
+        <v>10.58800495986426</v>
       </c>
     </row>
     <row r="29">
@@ -3455,106 +3409,102 @@
           <t>X &gt; 0.1129</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>317~317</t>
-        </is>
+      <c r="B29" t="n">
+        <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.449779345405162</v>
+        <v>1.462301635080784</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.730950211936175</v>
+        <v>1.743860021512226</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.806113051080914</v>
+        <v>4.819120182498516</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.14456807643289</v>
+        <v>7.157547218831354</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.659774621613089</v>
+        <v>5.672885425988028</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.903588799076381</v>
+        <v>6.916631695370747</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.080684734800947</v>
+        <v>8.093750989101423</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.244416162517879</v>
+        <v>8.257597171813117</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.498873689584784</v>
+        <v>8.512072428539547</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.595120744304481</v>
+        <v>8.608525871957312</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.28311189948218</v>
+        <v>10.2965691931924</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.26386729657524</v>
+        <v>11.27731958529535</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.52815527238113</v>
+        <v>10.54171131873274</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.77787660465742</v>
+        <v>10.76744696895927</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1242</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>253~253</t>
-        </is>
+          <t>X &gt; 0.1241</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>253</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.07573164026432977</v>
+        <v>0.08825392993995251</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.20724103125265</v>
+        <v>3.220150840828701</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.998143075644194</v>
+        <v>4.011150207061796</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.895194627224029</v>
+        <v>6.908173769622493</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.380488827171625</v>
+        <v>4.393599631546564</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.654215349867521</v>
+        <v>6.667258246161886</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.150509300579436</v>
+        <v>8.163575554879912</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.683325901797936</v>
+        <v>7.696506911093174</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.143742332563988</v>
+        <v>9.157147460216819</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.91527359322664</v>
+        <v>10.92873088693686</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.74017058456417</v>
+        <v>11.75362287328428</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.71517289061533</v>
+        <v>11.72872893696693</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.96489422289162</v>
+        <v>11.95446458719346</v>
       </c>
     </row>
     <row r="31">
@@ -3563,52 +3513,50 @@
           <t>X &gt; 0.1354</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>218~218</t>
-        </is>
+      <c r="B31" t="n">
+        <v>218</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.117291531219145</v>
+        <v>-1.104769241543522</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.317006415449619</v>
+        <v>2.32991622502567</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.298284497843852</v>
+        <v>3.311291629261454</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.639546804763285</v>
+        <v>6.652525947161749</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.807547608039741</v>
+        <v>3.82065841241468</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.563705142085674</v>
+        <v>4.576748038380039</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.313833810134497</v>
+        <v>6.326900064434973</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.305366007683268</v>
+        <v>6.318547016978506</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.703081717831239</v>
+        <v>6.716280456786002</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.229103321794142</v>
+        <v>7.242508449446973</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.31792797912793</v>
+        <v>9.331385272838148</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.7284579254642</v>
+        <v>10.74191021418431</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.22563450717985</v>
+        <v>11.23919055353146</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.55792464679558</v>
+        <v>10.54749501109743</v>
       </c>
     </row>
     <row r="32">
@@ -3617,52 +3565,50 @@
           <t>X &gt; 0.1467</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>176~176</t>
-        </is>
+      <c r="B32" t="n">
+        <v>176</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.925256502028155</v>
+        <v>-1.912734212352532</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6137557238655447</v>
+        <v>0.6267628552831468</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.584917947382138</v>
+        <v>3.597897089780602</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.7737694595826881</v>
+        <v>0.7868802639576273</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.652436111774534</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.827386770935163</v>
+        <v>3.840453025235639</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.496567008517296</v>
+        <v>4.509748017812534</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.140112576880455</v>
+        <v>6.153311315835218</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.85816921003434</v>
+        <v>5.871574337687171</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.062506794807675</v>
+        <v>9.075964088517892</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.23325358851675</v>
+        <v>10.24670587723686</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.94936261393547</v>
+        <v>10.96291866028707</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.494538491666304</v>
+        <v>9.484108855968152</v>
       </c>
     </row>
     <row r="33">
@@ -3671,52 +3617,50 @@
           <t>X &gt; 0.158</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>139~139</t>
-        </is>
+      <c r="B33" t="n">
+        <v>139</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.414301629562488</v>
+        <v>-1.401779339886865</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.010095980494825</v>
+        <v>2.023005790070876</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.8958028134665881</v>
+        <v>0.9088099448841902</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.90375378780071</v>
+        <v>3.916732930199174</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4876347310019185</v>
+        <v>0.5007455353768577</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7850766687175792</v>
+        <v>0.7981195650119446</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.736314174466884</v>
+        <v>5.74938042876736</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.549706315253722</v>
+        <v>4.56288732454896</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.646979810366396</v>
+        <v>6.660178549321159</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.235703546201769</v>
+        <v>7.2491086738546</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.908648063610812</v>
+        <v>9.92210535732103</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.38188014181955</v>
+        <v>11.39533243053966</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.40047445173796</v>
+        <v>12.41403049808956</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.21134686315094</v>
+        <v>11.20091722745278</v>
       </c>
     </row>
     <row r="34">
@@ -3725,52 +3669,50 @@
           <t>X &gt; 0.1692</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>108~108</t>
-        </is>
+      <c r="B34" t="n">
+        <v>108</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.6415864683581276</v>
+        <v>-0.6290641786825049</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.4013082294705228</v>
+        <v>-0.3883984198944717</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.204345018531782</v>
+        <v>-1.191234214156843</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9069030808161216</v>
+        <v>-0.8938601845217562</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.712066905615295</v>
+        <v>2.725133159915771</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.096735358685642</v>
+        <v>4.10991636798088</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.961661398429271</v>
+        <v>4.974860137384034</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.963388065253199</v>
+        <v>5.97679319290603</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.462338444639329</v>
+        <v>9.475795738349547</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.34857345383661</v>
+        <v>11.36202574255672</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.92831884289171</v>
+        <v>10.94187488924331</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.326188323316146</v>
+        <v>9.315758687617993</v>
       </c>
     </row>
     <row r="35">
@@ -3779,52 +3721,50 @@
           <t>X &gt; 0.1805</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.874390701162362</v>
+        <v>-4.861868411486739</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3922772547414439</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
   </sheetData>
@@ -3875,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3964,55 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1464</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+          <t>X &lt; -0.1463</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.55418072740908</v>
+        <v>16.5667030170847</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.37117854301625</v>
+        <v>11.3840883525923</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.54773840784823</v>
+        <v>14.56074553926583</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15.8684677309319</v>
+        <v>15.88144687333037</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.94909413490737</v>
+        <v>12.96220493928231</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.484631310718264</v>
+        <v>8.497674207012629</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.78084997439837</v>
+        <v>10.79391622869885</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.31366657561687</v>
+        <v>10.32684758491211</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.212065313930452</v>
+        <v>8.225470441583283</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.299733296861106</v>
+        <v>4.289303661162954</v>
       </c>
     </row>
     <row r="7">
@@ -4021,52 +3959,50 @@
           <t>X &lt; -0.1351</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>99~99</t>
-        </is>
+      <c r="B7" t="n">
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.16312733635569</v>
+        <v>13.17564962603131</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.521250693088398</v>
+        <v>8.534160502664449</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.17688703699686</v>
+        <v>13.18989416841446</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.30714016960436</v>
+        <v>13.32011931200282</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.76871895453219</v>
+        <v>12.78182975890713</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.015655841742799</v>
+        <v>8.028698738037164</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.920821114369502</v>
+        <v>6.933887368669978</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.453637715588002</v>
+        <v>6.46681872488324</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.372435809203679</v>
+        <v>4.385634548158443</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.53241163427677</v>
+        <v>4.545816761929601</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.317557299858173</v>
+        <v>3.331014593568391</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.372142477405625</v>
+        <v>5.385594766125735</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.94178685635972</v>
+        <v>3.955342902711322</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.191508188636007</v>
+        <v>4.181078552937855</v>
       </c>
     </row>
     <row r="8">
@@ -4075,106 +4011,102 @@
           <t>X &lt; -0.1238</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B8" t="n">
+        <v>122</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.14292531615366</v>
+        <v>11.45351019897385</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.704905422197669</v>
+        <v>9.022651974762475</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.92160696353497</v>
+        <v>14.36558550804022</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14.22541381515074</v>
+        <v>14.49581065162858</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.86054631908682</v>
+        <v>13.13784896738535</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.546418008868592</v>
+        <v>6.877845947840107</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.80879172961285</v>
+        <v>5.153791326278856</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.341608330831349</v>
+        <v>4.686722682492118</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.627715882665569</v>
+        <v>2.986396263674258</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.256929540612852</v>
+        <v>4.595493860787023</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.052176216295273</v>
+        <v>4.390792702526831</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.739451935624182</v>
+        <v>6.064515117177237</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.31919732467928</v>
+        <v>5.644364263863828</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.395364937947299</v>
+        <v>6.689772045237902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1126</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>158~158</t>
-        </is>
+          <t>X &lt; -0.1125</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.898966743081168</v>
+        <v>8.911489032756791</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.1861273073321</v>
+        <v>9.199037116908151</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.85454973997601</v>
+        <v>13.86755687139361</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13.98480287258351</v>
+        <v>13.99778201498197</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.44638165751134</v>
+        <v>13.45949246188628</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.414709671176368</v>
+        <v>7.427752567470733</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.697064561499033</v>
+        <v>6.710130815799509</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.862792555122589</v>
+        <v>6.875973564417826</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.637235706914979</v>
+        <v>3.650434445869742</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.95166748391236</v>
+        <v>5.965072611565191</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.481091374784661</v>
+        <v>4.494548668494879</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.047120101750345</v>
+        <v>7.060572390470455</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.626865490805443</v>
+        <v>6.640421537157046</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.509498215486786</v>
+        <v>7.499068579788634</v>
       </c>
     </row>
     <row r="10">
@@ -4183,916 +4115,882 @@
           <t>X &lt; -0.1013</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>210~210</t>
-        </is>
+      <c r="B10" t="n">
+        <v>210</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.982752155980499</v>
+        <v>7.995274445656122</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.847369019206724</v>
+        <v>6.860278828782775</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.39227725474144</v>
+        <v>10.4052563971399</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.901475087288311</v>
+        <v>8.914585891663251</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.341774167861125</v>
+        <v>6.35481706415549</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.443142879910752</v>
+        <v>1.456341618865515</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.497779599644737</v>
+        <v>2.511184727297568</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.232171337434487</v>
+        <v>4.245623626154597</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.811916726489585</v>
+        <v>3.825472772841188</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.09001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>265~265</t>
-        </is>
+          <t>X &lt; -0.08998</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>265</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.764270303625402</v>
+        <v>7.777277435043004</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.894523436232902</v>
+        <v>7.907502578631366</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.488177692858848</v>
+        <v>8.501288497233787</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.634676234348092</v>
+        <v>4.647719130642457</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.417867045377697</v>
+        <v>3.430933299678173</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.195966665464127</v>
+        <v>2.209147674759365</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.00289130758371</v>
+        <v>1.016090046538473</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5301246131218207</v>
+        <v>0.5435297407746518</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.561421164025951</v>
+        <v>-1.547963870315733</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.737112936715711</v>
+        <v>0.750565225435821</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4378586553612678</v>
+        <v>-0.4243026090096649</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1881373230849803</v>
+        <v>-0.1985669587831325</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07874</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>348~348</t>
-        </is>
+          <t>X &lt; -0.07871</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>348</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.690469725767045</v>
+        <v>4.702992015442668</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.653608756480942</v>
+        <v>3.666518566056993</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.707015911953313</v>
+        <v>6.720023043370915</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.411981688238974</v>
+        <v>7.424960830637438</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.735629438684043</v>
+        <v>7.748740243058982</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.584795514330743</v>
+        <v>4.597838410625108</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.350636509702142</v>
+        <v>3.363702764002618</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.02138414540341</v>
+        <v>2.034565154698647</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.960384259221108</v>
+        <v>1.973582998175871</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.03916621316315627</v>
+        <v>-0.02576108551032519</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.255413790354289</v>
+        <v>-2.241956496644072</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.4968927019743745</v>
+        <v>-0.4834404132542645</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.491859956597445</v>
+        <v>-1.478303910245842</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.816851267999311</v>
+        <v>-1.827280903697464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06747</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>442~443</t>
-        </is>
+          <t>X &lt; -0.06744</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>443</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.52010569784872</v>
+        <v>5.532627987524343</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.134265719195973</v>
+        <v>4.147175528772024</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.770999721402994</v>
+        <v>5.784006852820596</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.126986488322004</v>
+        <v>6.139965630720468</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.588565273249834</v>
+        <v>5.601676077624774</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.854404502161884</v>
+        <v>3.86744739845625</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.866736247643551</v>
+        <v>2.879802501944027</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.722351945927514</v>
+        <v>1.735532955222752</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7584175224991654</v>
+        <v>0.7716162614539286</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.671843102709346</v>
+        <v>-1.658437975056515</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.779530964272972</v>
+        <v>-2.766073670562754</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.390746001058467</v>
+        <v>-1.377293712338357</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.811000612003369</v>
+        <v>-1.797444565651766</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.115909883487952</v>
+        <v>-2.02317618404826</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05619</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>549~550</t>
-        </is>
+          <t>X &lt; -0.05617</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>550</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.688379861608205</v>
+        <v>3.700902151283827</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.985897157734861</v>
+        <v>2.998806967310912</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.318301178410991</v>
+        <v>3.331308309828593</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.721281583745771</v>
+        <v>2.734260726144235</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.091951277764501</v>
+        <v>3.10506208213944</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.571211397298349</v>
+        <v>1.584254293592714</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.12284131638971</v>
+        <v>1.135907570690186</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.405341968574092</v>
+        <v>-1.392143229619329</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.800921699056566</v>
+        <v>-2.787516571403735</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.187493205192332</v>
+        <v>-3.174035911482115</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.062200956937801</v>
+        <v>-2.048748668217691</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.937001022428163</v>
+        <v>-1.92344497607656</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.951893036732436</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04492</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>711~712</t>
-        </is>
+          <t>X &lt; -0.0449</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>712</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.141393140464189</v>
+        <v>2.153915430139811</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.653415033117895</v>
+        <v>1.666324842693946</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.38214183213929</v>
+        <v>2.395148963556892</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.652844402949036</v>
+        <v>2.6658235453475</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.097569255292598</v>
+        <v>3.110680059667537</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.569168496379049</v>
+        <v>1.582211392673415</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.063086464500017</v>
+        <v>1.076152718800493</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5276924398994467</v>
+        <v>-0.5145114306042089</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3077934496772627</v>
+        <v>-0.2945947107224995</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.579266949311929</v>
+        <v>-1.565861821659098</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.205368588236247</v>
+        <v>-2.19191129452603</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.749637116284077</v>
+        <v>-1.736184827563967</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.888992850824486</v>
+        <v>-1.875436804472884</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.562231742319121</v>
+        <v>-1.509251716044105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03365</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>914~916</t>
-        </is>
+          <t>X &lt; -0.03363</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>915</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.218352072803128</v>
+        <v>1.230874362478751</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.916822127961133</v>
+        <v>0.9297319375371842</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.504486172456247</v>
+        <v>1.517493303873849</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.416398693710043</v>
+        <v>1.429377836108507</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.297191452436998</v>
+        <v>2.310302256811937</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.9570788049998242</v>
+        <v>0.9701217012941896</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1101876633641581</v>
+        <v>-0.09712140906368205</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.014052284853079</v>
+        <v>-1.000871275557841</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8567115596816777</v>
+        <v>-0.8435128207269145</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.81600705038646</v>
+        <v>-1.802601922733629</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.45744159741146</v>
+        <v>-2.443984303701242</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.532228745742884</v>
+        <v>-2.518776457022774</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.893781946422202</v>
+        <v>-2.938927310336183</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.25700318328893</v>
+        <v>-2.217331779898714</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02238</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1137~1140</t>
-        </is>
+          <t>X &lt; -0.02236</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1139</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.190772206105812</v>
+        <v>1.243886774023053</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4563915755976993</v>
+        <v>0.5091248702668452</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9387158514572462</v>
+        <v>0.9907776748194408</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8058110893279107</v>
+        <v>0.7704331426847446</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.232302154957488</v>
+        <v>1.283852616758196</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.03851602249771702</v>
+        <v>0.09130552457033048</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5725334842482468</v>
+        <v>-0.5192593482804213</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.478313374257823</v>
+        <v>-1.424540086720967</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.627032558685734</v>
+        <v>-1.573164662174499</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.301719147222435</v>
+        <v>-2.24779862064284</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.155595278557556</v>
+        <v>-2.101930103179988</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.249286917509281</v>
+        <v>-2.242836788686184</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.094853714551505</v>
+        <v>-2.089314194577355</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.797138169403489</v>
+        <v>-1.727879331437066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01111</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1463~1466</t>
-        </is>
+          <t>X &lt; -0.01109</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1464</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4397131122593265</v>
+        <v>0.4161528174547371</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.0804553165303048</v>
+        <v>-0.06754550695425365</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.002165744949500947</v>
+        <v>0.01517287636710307</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2688445255788352</v>
+        <v>0.2818236679772994</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4807643746267161</v>
+        <v>0.4938751790016553</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0278652482223265</v>
+        <v>0.04090814451669189</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5343582371263551</v>
+        <v>-0.5212919828258791</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.342605755962424</v>
+        <v>-1.329424746667186</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.471818466155639</v>
+        <v>-1.458619727200876</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.117305179150833</v>
+        <v>-2.103900051498002</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.844568735392009</v>
+        <v>-1.831111441681792</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.387363848653607</v>
+        <v>-2.410648705424691</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.224383039318376</v>
+        <v>-2.247987327922665</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.937450571901699</v>
+        <v>-1.916785331811276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001635</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1903~1910</t>
-        </is>
+          <t>X &lt; 0.0001758</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1904</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5039095243984519</v>
+        <v>-0.5185926396395359</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5971585300328712</v>
+        <v>-0.5842487204568201</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3877800635529098</v>
+        <v>-0.403103874845371</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1615406437010094</v>
+        <v>0.1745197860994736</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4902741289175481</v>
+        <v>0.4743653822965967</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8692044372945347</v>
+        <v>0.8531698643950776</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3691737477281336</v>
+        <v>-0.3561074934276576</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7839187616118863</v>
+        <v>-0.7707377523166485</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9497954175896837</v>
+        <v>-0.9365966786349205</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.537728678128879</v>
+        <v>-1.524323550476048</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.713869242586199</v>
+        <v>-1.72902470873624</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.333257983900339</v>
+        <v>-2.348090459689601</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.884861984995005</v>
+        <v>-1.900061535370284</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.079292301817674</v>
+        <v>-2.065738355643767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.01144</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2292~2301</t>
-        </is>
+          <t>X &lt; 0.01145</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2293</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5594965557597362</v>
+        <v>-0.5695346230625873</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9310988896959742</v>
+        <v>-0.9412981253365587</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3893978211540343</v>
+        <v>-0.3999169866140946</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.757791127702923</v>
+        <v>-0.7681316183533724</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3151013996408025</v>
+        <v>-0.3257473173383616</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1245440667497988</v>
+        <v>-0.1352217027661737</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.6448178537084885</v>
+        <v>-0.6317515994080125</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6329071758349372</v>
+        <v>-0.6197261665396994</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9116770968604442</v>
+        <v>-0.898478357905681</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.674694267951082</v>
+        <v>-1.661289140298251</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.725025389783333</v>
+        <v>-1.735328277652528</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.97200518932268</v>
+        <v>-1.982200836963983</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.583593418257365</v>
+        <v>-1.594048130550689</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.746140550059849</v>
+        <v>-1.736800631404478</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02271</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2641~2651</t>
-        </is>
+          <t>X &lt; 0.02272</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2642</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5130535597422323</v>
+        <v>-0.5201317168088551</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.671049669023283</v>
+        <v>-0.6782960126966273</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.06424455068059842</v>
+        <v>-0.0717791687305791</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.04880149585783045</v>
+        <v>0.0412376299501318</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3242897741755328</v>
+        <v>0.3165424446772178</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3024695571279423</v>
+        <v>0.294767052462106</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.1017677229641265</v>
+        <v>-0.10933396026563</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5311439383807937</v>
+        <v>-0.5179629290855559</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.781179741387291</v>
+        <v>-0.7679810024325278</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.102004359307472</v>
+        <v>-1.088599231654641</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.096859179611258</v>
+        <v>-1.104264473090637</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.419955574624325</v>
+        <v>-1.427238559566888</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.251707512002177</v>
+        <v>-1.259117249319779</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.283920081188327</v>
+        <v>-1.277366610276424</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.03398</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2925~2936</t>
-        </is>
+          <t>X &lt; 0.03399</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2926</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8245009905097049</v>
+        <v>-0.8295711207624734</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.476391830959578</v>
+        <v>-0.4817479001649403</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2394852750809804</v>
+        <v>-0.2449655015389069</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1248269616467894</v>
+        <v>-0.1303361629925419</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.003274606550320414</v>
+        <v>-0.002336485879652628</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.08996536520901799</v>
+        <v>-0.09551750350514254</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6339070546931396</v>
+        <v>-0.6392855064476279</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.9304419893108147</v>
+        <v>-0.9172609800155769</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.162090339656942</v>
+        <v>-1.148891600702179</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.071941904525389</v>
+        <v>-1.077308690547383</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.292063498287213</v>
+        <v>-1.297379280301747</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.512211827515813</v>
+        <v>-1.517452095937522</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.29858680506657</v>
+        <v>-1.303946265016521</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.269253272125461</v>
+        <v>-1.264353208283374</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.04525</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3150~3163</t>
-        </is>
+          <t>X &lt; 0.04526</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3151</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.054930574399037</v>
+        <v>-1.058665714478721</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8792054815613355</v>
+        <v>-0.8831233060199395</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8776092066800274</v>
+        <v>-0.8815604153740964</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.667095861593701</v>
+        <v>-0.6711058149388549</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3971275446476454</v>
+        <v>-0.4012670317845988</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5257429466477674</v>
+        <v>-0.5298209315936191</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.005128274994512</v>
+        <v>-1.009063354521402</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.328556853678805</v>
+        <v>-1.332428098753823</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.404189396898545</v>
+        <v>-1.408043678979858</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.476312256501657</v>
+        <v>-1.480212148409933</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.600317932003726</v>
+        <v>-1.604196746208579</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.834120661598632</v>
+        <v>-1.83792492171365</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.538916720186442</v>
+        <v>-1.542849683044714</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.684393687265874</v>
+        <v>-1.680456505677498</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.05652</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3316~3329</t>
-        </is>
+          <t>X &lt; 0.05653</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3317</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7061147996332338</v>
+        <v>-0.7091442587625849</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8898677024050059</v>
+        <v>-0.892943217019635</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.178570149839949</v>
+        <v>-1.18158504681476</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.062351499947447</v>
+        <v>-1.065394983340148</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8027855643407591</v>
+        <v>-0.8059421271209288</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.729740358527053</v>
+        <v>-0.7329022340901261</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.249658888791814</v>
+        <v>-1.252671359404985</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.429832750663913</v>
+        <v>-1.432821675509487</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.534875789164822</v>
+        <v>-1.537838593857749</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.525456200699502</v>
+        <v>-1.528476304233386</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.532997053558489</v>
+        <v>-1.536029339740601</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.723223478719817</v>
+        <v>-1.726198064257034</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.524086833813044</v>
+        <v>-1.527149288641631</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.55930513153799</v>
+        <v>-1.55612465185655</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.06779</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3456~3469</t>
-        </is>
+          <t>X &lt; 0.0678</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3457</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9223803784400175</v>
+        <v>-0.9247200651164817</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.990825081963159</v>
+        <v>-0.9932263668959536</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.226156959355478</v>
+        <v>-1.228511339956455</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.167088557365282</v>
+        <v>-1.169454825682081</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7954946096813771</v>
+        <v>-0.7979961982990957</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9443250293235224</v>
+        <v>-0.9467702374318137</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.18682187632286</v>
+        <v>-1.189202653958141</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.349698943901167</v>
+        <v>-1.352057300749927</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.395150484242194</v>
+        <v>-1.397500091128705</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.275961110512171</v>
+        <v>-1.27838888891575</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.349232015673543</v>
+        <v>-1.35165020470334</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.414637993585366</v>
+        <v>-1.417036928093118</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.44298361374485</v>
+        <v>-1.445396708554604</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.408765380387564</v>
+        <v>-1.406179623270276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.07906</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3592~3605</t>
-        </is>
+          <t>X &lt; 0.07907</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3593</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.870692134356986</v>
+        <v>-0.8724856367462266</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7753781928856611</v>
+        <v>-0.7772616242916683</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.155445446876008</v>
+        <v>-1.157239768064649</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.12143206018942</v>
+        <v>-1.12323176748481</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8397343651124629</v>
+        <v>-0.8416341977050834</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8606067845198311</v>
+        <v>-0.8624902975562065</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.097118773534262</v>
+        <v>-1.098940914158298</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.243680098461326</v>
+        <v>-1.245480707338388</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.345291926872669</v>
+        <v>-1.347067682598258</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.234939294364487</v>
+        <v>-1.236779846355084</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.313172810705034</v>
+        <v>-1.315000619743813</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.319144347437117</v>
+        <v>-1.320970188005276</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.334465789778818</v>
+        <v>-1.336304792943054</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.292057985353338</v>
+        <v>-1.289997360665197</v>
       </c>
     </row>
     <row r="27">
@@ -5101,52 +4999,50 @@
           <t>X &lt; 0.09034</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3688~3701</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3689</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6696069232902246</v>
+        <v>-0.6710835075737904</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5104173385796429</v>
+        <v>-0.5119886407557104</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9448657708873469</v>
+        <v>-0.9463329678126797</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.989421990667914</v>
+        <v>-0.990873831107109</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6478377403582911</v>
+        <v>-0.649399789142322</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8227279966410492</v>
+        <v>-0.8242341614199447</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.001159175675738</v>
+        <v>-1.002620567837951</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.074814100898458</v>
+        <v>-1.076271172739801</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.148246234630271</v>
+        <v>-1.149686173951665</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.062814735597492</v>
+        <v>-1.064305582555058</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.035920583828322</v>
+        <v>-1.037426042477875</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.149168190246499</v>
+        <v>-1.150642710236369</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.093658406789537</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.01867389247883</v>
+        <v>-1.017012413654065</v>
       </c>
     </row>
     <row r="28">
@@ -5155,52 +5051,50 @@
           <t>X &lt; 0.1016</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3780~3793</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3781</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2656502896273167</v>
+        <v>-0.2668938903129501</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1756870386594684</v>
+        <v>-0.1769953479588509</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5299518610844629</v>
+        <v>-0.5311773058215792</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7020813330208426</v>
+        <v>-0.7032587578009952</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5401416227369467</v>
+        <v>-0.5413759125835043</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5715360347838256</v>
+        <v>-0.5727552315878341</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7740307579315342</v>
+        <v>-0.7751992738907916</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8307753532941646</v>
+        <v>-0.8319412540985454</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8774207484468022</v>
+        <v>-0.878576500521703</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.867517893559743</v>
+        <v>-0.8686982694942813</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9255077679491563</v>
+        <v>-0.9266786176131916</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9293708045412856</v>
+        <v>-0.9305404159888226</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9118273069608804</v>
+        <v>-0.9130127853165035</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9383619412341204</v>
+        <v>-0.9370159066006707</v>
       </c>
     </row>
     <row r="29">
@@ -5209,106 +5103,102 @@
           <t>X &lt; 0.1129</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3848~3861</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3849</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.09768592445757918</v>
+        <v>-0.09873063436656082</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.01174768446956875</v>
+        <v>-0.01284804434410347</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3148586133391049</v>
+        <v>-0.3158890523946738</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.481602623804072</v>
+        <v>-0.4825877272940104</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3578801974753105</v>
+        <v>-0.3589088872747581</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4352955812003358</v>
+        <v>-0.4362986561798365</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.505976040054108</v>
+        <v>-0.5069630441721387</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5439457998989923</v>
+        <v>-0.5449330339502296</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.538862483875036</v>
+        <v>-0.5398528111638896</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5440539562075131</v>
+        <v>-0.5450608698252779</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6824531919726269</v>
+        <v>-0.6834289068564132</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7634996582365048</v>
+        <v>-0.7644541520353556</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.701686064587868</v>
+        <v>-0.702665755297339</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7492717521439332</v>
+        <v>-0.7481828845075356</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1242</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3912~3925</t>
-        </is>
+          <t>X &lt; 0.1241</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3913</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01611581991741673</v>
+        <v>0.01526328683701905</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.07850836538625572</v>
+        <v>-0.07936327009499422</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1792076853991702</v>
+        <v>-0.180043742807861</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3410706484177837</v>
+        <v>-0.3418637611451771</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1771127365175573</v>
+        <v>-0.177956785785085</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2993822947239124</v>
+        <v>-0.3001907691231978</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3702575724734061</v>
+        <v>-0.3710497576957152</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3641573870463048</v>
+        <v>-0.3649591199081215</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3856376494059006</v>
+        <v>-0.3864353081380614</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4301351822026405</v>
+        <v>-0.4309357001432659</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5440472514015511</v>
+        <v>-0.5448224283360474</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5976215914897622</v>
+        <v>-0.5983829419899038</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5947618662355154</v>
+        <v>-0.5955311933850567</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6374563029051714</v>
+        <v>-0.6365844042599917</v>
       </c>
     </row>
     <row r="31">
@@ -5317,52 +5207,50 @@
           <t>X &lt; 0.1354</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3947~3960</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3948</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.08231925554760267</v>
+        <v>0.08156819062191545</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.000440071593025948</v>
+        <v>-0.001193032689094764</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1037209631664737</v>
+        <v>-0.10445370537267</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2629810578330236</v>
+        <v>-0.2636721141332288</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1052175796672401</v>
+        <v>-0.1059563661799814</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.122616898299853</v>
+        <v>-0.1233475080434587</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1935701426621108</v>
+        <v>-0.1942843612716558</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2169129721648062</v>
+        <v>-0.217628172006755</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2134023292660316</v>
+        <v>-0.2141196341912348</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2396828872482786</v>
+        <v>-0.2404057874508467</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3543516631900232</v>
+        <v>-0.355048773588365</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4324212658767692</v>
+        <v>-0.4330984956054991</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4585999908356442</v>
+        <v>-0.4592768322426721</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4479955387825996</v>
+        <v>-0.4472718200933699</v>
       </c>
     </row>
     <row r="32">
@@ -5371,52 +5259,50 @@
           <t>X &lt; 0.1467</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3989~4002</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3990</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1052623294651909</v>
+        <v>0.1046447988436086</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1064352050412083</v>
+        <v>0.1057989258770817</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.05011936022917496</v>
+        <v>0.04949240016964751</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.05604911256467204</v>
+        <v>-0.05664836476485391</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.06944002213668909</v>
+        <v>0.06880301737325567</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05539271510488675</v>
+        <v>0.05476227485608121</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.01566082211243014</v>
+        <v>-0.01627474786691607</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.0686565664058989</v>
+        <v>-0.06926281119828559</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1158622945175551</v>
+        <v>-0.1164577136334373</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1006963046162994</v>
+        <v>-0.1013054365195956</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2413281478048219</v>
+        <v>-0.2419046818302206</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2931296373778878</v>
+        <v>-0.2936931025408924</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3234216193750754</v>
+        <v>-0.3239825492525696</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2851966891719044</v>
+        <v>-0.2846311759297748</v>
       </c>
     </row>
     <row r="33">
@@ -5425,52 +5311,50 @@
           <t>X &lt; 0.158</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4026~4039</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4027</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.06907715391728431</v>
+        <v>0.06858891996069616</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.05546354973809997</v>
+        <v>0.0549639818734704</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.04507299981914059</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03365129308997439</v>
+        <v>-0.03413164442797267</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.08575549089957235</v>
+        <v>0.08524047658939793</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.09935851047274014</v>
+        <v>0.09884255539287068</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.04619594439066788</v>
+        <v>-0.04667682557790442</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.02859532914504115</v>
+        <v>-0.02908501872692426</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.0759177336673531</v>
+        <v>-0.07639647637257951</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.09350008840915081</v>
+        <v>-0.09398237055125236</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1850788907899314</v>
+        <v>-0.1855405358899631</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2360747494809132</v>
+        <v>-0.2365236631408649</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2699355326658761</v>
+        <v>-0.2703800668051031</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2545921591036873</v>
+        <v>-0.2541352689161442</v>
       </c>
     </row>
     <row r="34">
@@ -5479,52 +5363,50 @@
           <t>X &lt; 0.1692</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4057~4070</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03727421050255941</v>
+        <v>0.03689286162973104</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1343589196151456</v>
+        <v>0.1339421024460421</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.04780864243173966</v>
+        <v>0.04741009941281504</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.005231146209304427</v>
+        <v>-0.005615916387277764</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1337614105731646</v>
+        <v>0.1333384529287258</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1495408169561827</v>
+        <v>0.1491158953456093</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07828154545198629</v>
+        <v>0.07787335398437989</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.01837691163412103</v>
+        <v>0.01797994336730113</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.02019851752769597</v>
+        <v>0.01980047521140449</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.00371545787101013</v>
+        <v>-0.004113858902059064</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.09613628624919812</v>
+        <v>-0.09651358155888801</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1464581631462281</v>
+        <v>-0.1468230076713439</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1339632519187361</v>
+        <v>-0.1343343576976537</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1167954541512444</v>
+        <v>-0.1164556854539569</v>
       </c>
     </row>
     <row r="35">
@@ -5533,52 +5415,50 @@
           <t>X &lt; 0.1805</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4082</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1201425298144443</v>
+        <v>0.1198165701982532</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1095006492836177</v>
+        <v>0.109168027842955</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.04525451510145473</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.091384470348288</v>
+        <v>0.09105447003474865</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1286260943904267</v>
+        <v>0.1282837883237562</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1216015793833236</v>
+        <v>0.1212625176425064</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.09918004615309428</v>
+        <v>0.09884583076710385</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.06135669644131525</v>
+        <v>0.06102892868248233</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.06281982557888455</v>
+        <v>0.06249119883452181</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.03406216652705041</v>
+        <v>0.0337355978660554</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.05900954389769453</v>
+        <v>-0.05931464743404291</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.05984083848657917</v>
+        <v>-0.06014569430620043</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.04986904612420773</v>
+        <v>-0.05017888385381752</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.0313130153172807</v>
+        <v>-0.03105750633196891</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_14.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_14.xlsx
@@ -568,1145 +568,1145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1407</t>
+          <t>X ≈ -0.1403</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.796742361064148</v>
+        <v>-2.503144860213546</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.403916154416706</v>
+        <v>-10.31325824936962</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.497652519469618</v>
+        <v>1.757629524854295</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.021360956274528</v>
+        <v>-4.347034896369763</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.74537179444452</v>
+        <v>13.87261823007564</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.391732165292581</v>
+        <v>7.910772050964439</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-14.65717127656702</v>
+        <v>-10.86573249277468</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.12715246537748</v>
+        <v>-11.33354364937394</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.19166172170714</v>
+        <v>-11.3731354895309</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.04447864460778</v>
+        <v>-12.19894516063859</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.5911749822301</v>
+        <v>-6.160477281172092</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.895802921857594</v>
+        <v>-6.103870858513439</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.316557139761755</v>
+        <v>-0.2519555304811618</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.575017946880273</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1295</t>
+          <t>X ≈ -0.1291</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.026915097545213</v>
+        <v>-0.3361138324524191</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.09212629339153</v>
+        <v>11.0910643142297</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.37280907067588</v>
+        <v>19.37282506270689</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>19.50760354321748</v>
+        <v>19.5072644322063</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.63723894622274</v>
+        <v>10.3475371930862</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.920238160732701</v>
+        <v>-2.395127938958758</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.504058894262094</v>
+        <v>-6.796493587408214</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.971066642164779</v>
+        <v>-7.263321472714544</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.032606756475893</v>
+        <v>-7.301935714398297</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.804612466241089</v>
+        <v>0.5603196342712735</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.945864889825629</v>
+        <v>4.701094130964883</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.982394012742553</v>
+        <v>9.106045641303176</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.91132186275286</v>
+        <v>8.71322503184043</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>17.48806142513811</v>
+        <v>13.31223409774825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1182</t>
+          <t>X ≈ -0.1178</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2948539999098614</v>
+        <v>1.768879748794731</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.767102837788059</v>
+        <v>11.58600413683019</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.14548223466635</v>
+        <v>14.04502471070963</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.27854506549119</v>
+        <v>14.17820729408204</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14.51625130317891</v>
+        <v>16.54450147230552</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.272654481467278</v>
+        <v>11.11841131179736</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.96349038544354</v>
+        <v>13.91294642941702</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.27371344856952</v>
+        <v>16.3041331691117</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.893511948905534</v>
+        <v>7.710573801028524</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>10.59586490472059</v>
+        <v>12.5980207356067</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.8425591511539</v>
+        <v>6.687139719028472</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.43088135840978</v>
+        <v>12.45835009323844</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.01344738132967</v>
+        <v>12.06639711283524</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>12.31844527787378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1069</t>
+          <t>X ≈ -0.1066</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.193242425234587</v>
+        <v>4.880220851393013</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2459193433317068</v>
+        <v>-0.3891208366075745</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.557986478951705</v>
+        <v>-4.475905579875651</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5103400486692422</v>
+        <v>-0.6529222857752615</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.884795022642351</v>
+        <v>-4.836384046709334</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.088164516946101</v>
+        <v>2.827760838115417</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.084838912007449</v>
+        <v>0.9194690754434802</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.30143035760014</v>
+        <v>-1.394498674233276</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.203735129514115</v>
+        <v>-5.130589178338816</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.975335786639377</v>
+        <v>-7.804957441646863</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-10.10345185748547</v>
+        <v>-9.861297428914597</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.305374389433112</v>
+        <v>-4.252936578629708</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.726472043704511</v>
+        <v>-4.649031275233817</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.348058976199674</v>
+        <v>-8.104835145408785</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.09564</t>
+          <t>X ≈ -0.09535</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>55</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.680630890046203</v>
+        <v>5.651590971775065</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.263843599846808</v>
+        <v>4.075305024108602</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.05717629872634689</v>
+        <v>3.683268435584829</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.626356084586064</v>
+        <v>0.1866956044848322</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.906461387207564</v>
+        <v>8.768941976482935</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.866889303040175</v>
+        <v>-0.02851635944683295</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.766653457143782</v>
+        <v>-3.718742712669979</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.864713921298872</v>
+        <v>-7.815569030072858</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6639186156701484</v>
+        <v>1.225100315053041</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.962169632100633</v>
+        <v>-5.046619320402854</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.80200559722131</v>
+        <v>-8.885407719963055</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-12.58778334894003</v>
+        <v>-12.46416664164601</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-16.64646128565938</v>
+        <v>-16.49782082589522</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-14.60680023494094</v>
+        <v>-12.61661965719246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.08435</t>
+          <t>X ≈ -0.08408</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>83</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.275249885790764</v>
+        <v>-5.505102397680496</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.479609388329706</v>
+        <v>-5.88299354016258</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.333556735278108</v>
+        <v>2.131999602701306</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.867815656682232</v>
+        <v>4.665623865153599</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.332347415785797</v>
+        <v>4.178759383028009</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.428913672304148</v>
+        <v>3.250486793491831</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.143148381471704</v>
+        <v>3.19108467733227</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.474817905831387</v>
+        <v>0.3210592437590378</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.024176049727764</v>
+        <v>2.690821339274088</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.841317230838449</v>
+        <v>-4.149232251992039</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.454006691246576</v>
+        <v>-6.761960327561745</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.420964087762357</v>
+        <v>-4.297340750521087</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.842170270828561</v>
+        <v>-4.693524673403672</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.027391691676975</v>
+        <v>-8.060212209218193</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.07308</t>
+          <t>X ≈ -0.07283</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8.540477079461553</v>
+        <v>8.284451112986311</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.88826844483728</v>
+        <v>6.709311881166336</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.346731474994122</v>
+        <v>2.205945493319099</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.427463425804113</v>
+        <v>0.2797672930001411</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.259339290954486</v>
+        <v>-3.293494378802556</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.188743083209616</v>
+        <v>0.06482028004307239</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.10484697510902</v>
+        <v>0.004626097691094344</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6390204127245767</v>
+        <v>0.5690509938757842</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.626531501776171</v>
+        <v>-3.585864235205932</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.630813371290607</v>
+        <v>-7.499046587643228</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.681927230157186</v>
+        <v>-4.614621265454943</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.64900963291317</v>
+        <v>-6.618677879804217</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.965629660607739</v>
+        <v>-2.892927393010481</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.740771526807443</v>
+        <v>-3.675663705927221</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.0618</t>
+          <t>X ≈ -0.06157</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.871147290532086</v>
+        <v>-2.991910366422374</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.751027865618909</v>
+        <v>-1.765802345433464</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.804458990663029</v>
+        <v>-8.746516035044507</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-11.33635740628176</v>
+        <v>-11.44122546152072</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.214808430060579</v>
+        <v>-7.230832398772449</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.851934041862833</v>
+        <v>-6.959601315567177</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-6.072732632357663</v>
+        <v>-5.139987472270178</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.27259665705999</v>
+        <v>-9.38021874471427</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.33611742947253</v>
+        <v>-9.421224876008694</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.45346333547775</v>
+        <v>-6.486783210847626</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.858631453461875</v>
+        <v>-4.274276903935942</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.825844242163413</v>
+        <v>-3.274665956791331</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.444327855057196</v>
+        <v>-2.727587733338041</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.284795137234475</v>
+        <v>-1.536002161481058</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.05053</t>
+          <t>X ≈ -0.05032</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>162</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.088601024557178</v>
+        <v>-3.491167459036959</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.84873462400887</v>
+        <v>-2.662751577471838</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7820173662211261</v>
+        <v>1.247452390670809</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.42557650829928</v>
+        <v>4.461849326257784</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.120691689395649</v>
+        <v>4.577890686099892</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.571404914280684</v>
+        <v>2.720855527080822</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8715073161727815</v>
+        <v>2.04040453079358</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2102987529235207</v>
+        <v>1.282037898779308</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.427242053971057</v>
+        <v>4.668937246754084</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.579435898582474</v>
+        <v>2.947936533775554</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.142040994135485</v>
+        <v>2.125326790355025</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.674339499135975</v>
+        <v>-0.5507166771432566</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.711814871806283</v>
+        <v>-0.3289597502546613</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2521425469500542</v>
+        <v>0.537140163234028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03927</t>
+          <t>X ≈ -0.03907</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.992654262731655</v>
+        <v>-2.016424171890286</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.643341638538338</v>
+        <v>-2.128953219019074</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.547804363792309</v>
+        <v>-2.03359245385581</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.891343825680543</v>
+        <v>-3.862807070528561</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4830823535955773</v>
+        <v>-0.9244883700382118</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.168925208240665</v>
+        <v>-1.631139983045621</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.204830151912198</v>
+        <v>-5.12137734101762</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.708354431752802</v>
+        <v>-3.13727290128373</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.770412911214599</v>
+        <v>-3.174227799769902</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.641402581198641</v>
+        <v>-2.527679631293601</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.340820070658239</v>
+        <v>-3.711415950956351</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.276909684153907</v>
+        <v>-5.123006090116277</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.686291192188889</v>
+        <v>-6.989925125386343</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.70084412208827</v>
+        <v>-4.782395058261976</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02799</t>
+          <t>X ≈ -0.02781</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.298199677523804</v>
+        <v>1.68911048123659</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.204481614894021</v>
+        <v>-1.682406298848726</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.154761933508944</v>
+        <v>-1.633764968878715</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.915174631139969</v>
+        <v>-1.503689229578868</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.900031216977659</v>
+        <v>-3.086082777295097</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.494801401988269</v>
+        <v>-3.257912796204948</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.244716610462604</v>
+        <v>-1.744083572938351</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.160609813641024</v>
+        <v>-3.097794968063447</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.560905946081988</v>
+        <v>-4.467202058355909</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.07834031925637</v>
+        <v>-3.957848237537519</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7159672148487601</v>
+        <v>-0.6085133816098818</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.128486811378259</v>
+        <v>-0.9945184233859479</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.384996582365005</v>
+        <v>0.8313507557864526</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2714465183059147</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01673</t>
+          <t>X ≈ -0.01656</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.479647177179558</v>
+        <v>-3.26518079023797</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.084482237881886</v>
+        <v>-2.145478088204612</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.399529053215701</v>
+        <v>-4.045198805914644</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.429799009083318</v>
+        <v>-2.411043231773014</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.27455829918263</v>
+        <v>-3.20225584482035</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1354277515958984</v>
+        <v>-1.123345322730657</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5267189885125276</v>
+        <v>-1.184871539540843</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.99298039311455</v>
+        <v>-1.652705593369561</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.054424083042377</v>
+        <v>-1.087839564519143</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.596743089102105</v>
+        <v>-1.613446221853742</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8796337589477972</v>
+        <v>-0.01146166611898991</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.999797619266715</v>
+        <v>-2.362041684838445</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.80456385719544</v>
+        <v>-2.283952319797613</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.578828206968907</v>
+        <v>-2.337320642953678</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.005457</t>
+          <t>X ≈ -0.005314</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>440</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.628953506005388</v>
+        <v>-3.18644963592137</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.306433064699036</v>
+        <v>-2.271684778580422</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.797144154675536</v>
+        <v>-0.8497082310653283</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1813952878968266</v>
+        <v>0.188265578742687</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4124458398711255</v>
+        <v>0.8350576790222561</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.556605688581584</v>
+        <v>4.061066125827324</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1928506178615521</v>
+        <v>0.3658176026526263</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.086650394985831</v>
+        <v>1.263394674055029</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7984398478454509</v>
+        <v>0.3177657757010124</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.400564703434803</v>
+        <v>-0.05119473232559102</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.395607902199529</v>
+        <v>-2.299901818630651</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.139657759126735</v>
+        <v>-2.695948695654415</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7416267942583801</v>
+        <v>-1.273581344803745</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.561345689486387</v>
+        <v>-2.843892384465185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.005813</t>
+          <t>X ≈ 0.005936</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8223863480152218</v>
+        <v>-0.9777161124544094</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.695648410849103</v>
+        <v>-2.570364921138093</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3846827541523155</v>
+        <v>-0.6464448774109925</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.384640213263815</v>
+        <v>-5.270598698611465</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.243665199624878</v>
+        <v>-3.956407767371211</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.973600068694488</v>
+        <v>-4.71295492559193</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.977606317134736</v>
+        <v>-1.9415219047333</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.121789850138434</v>
+        <v>0.1680279449265782</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.7097188000152812</v>
+        <v>-0.3850922208840188</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.330658912375696</v>
+        <v>-1.985534873727225</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.766230349434906</v>
+        <v>-1.417390963838514</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1894357446374215</v>
+        <v>-0.07170383123901303</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.09544778047010283</v>
+        <v>0.04848821986490748</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.1267815389839342</v>
+        <v>0.1903156755161248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.01708</t>
+          <t>X ≈ 0.01719</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1960408797551878</v>
+        <v>-0.07657160504492566</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.050422716919854</v>
+        <v>1.206702503001999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.085835224116181</v>
+        <v>1.834812182102226</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.361396766677011</v>
+        <v>5.41297208538581</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.537137195398564</v>
+        <v>4.06165397891678</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.119120288699868</v>
+        <v>2.322945244862083</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.31971234554122</v>
+        <v>3.124358121153861</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1532505175383392</v>
+        <v>-0.2150378576203238</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.09228964987461552</v>
+        <v>-0.2520104667570848</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.678809142833458</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.047375914514248</v>
+        <v>2.743009010639035</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.222155213001379</v>
+        <v>1.939106782486618</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9424055058197993</v>
+        <v>0.6818798904055612</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.741207058625093</v>
+        <v>1.505637396098983</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.02835</t>
+          <t>X ≈ 0.02845</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.717875989975248</v>
+        <v>-3.575159765840304</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.34618836679185</v>
+        <v>1.345307581185232</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.859451181810236</v>
+        <v>-1.504570758006665</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.728726981061143</v>
+        <v>-1.725563909774479</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.970232632279348</v>
+        <v>-2.565690243708772</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.727121310522179</v>
+        <v>-3.345536303837221</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.571181940141386</v>
+        <v>-5.511455550957457</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.634188909196602</v>
+        <v>-4.573779539411014</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.701423290630231</v>
+        <v>-4.610752148547768</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.9840489699680006</v>
+        <v>-0.8731772205908186</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.095930917884161</v>
+        <v>-3.182580826021606</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.357327413416165</v>
+        <v>-2.422659702691845</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.721140238560594</v>
+        <v>-1.765186050308294</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.143291912277682</v>
+        <v>-1.165263995310397</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.03963</t>
+          <t>X ≈ 0.0397</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>225</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.076550312158979</v>
+        <v>-3.621222935998098</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.1422005311845</v>
+        <v>-5.648844465598394</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-9.20077581645851</v>
+        <v>-9.153693565024263</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.734354573388963</v>
+        <v>-7.690476190476147</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.608124534428839</v>
+        <v>-5.513058664761544</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.199639393682588</v>
+        <v>-6.129162034831459</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.852787756169427</v>
+        <v>-5.745373679612428</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.773604834380855</v>
+        <v>-6.655650884440163</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.803305619025117</v>
+        <v>-4.914845715799231</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.726910510797723</v>
+        <v>-7.072007629947599</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.59827833572453</v>
+        <v>-5.942814744150354</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.008344627813656</v>
+        <v>-6.329092451229855</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.650717703349287</v>
+        <v>-4.946472600015902</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.091648719789418</v>
+        <v>-7.364094404667256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.05089</t>
+          <t>X ≈ 0.05095</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>166</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5.952818909224689</v>
+        <v>5.923623114872058</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.080053930827091</v>
+        <v>-1.081240717271747</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.896512062570018</v>
+        <v>-6.896665452574339</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.573515834644375</v>
+        <v>-8.574010327022378</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.509395749185785</v>
+        <v>-8.460849829420013</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.887093524600033</v>
+        <v>-5.839081845609712</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.342113975615788</v>
+        <v>-3.292866413222072</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.005505770692714</v>
+        <v>-3.932248660913018</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.445786012805705</v>
+        <v>-2.346438687511132</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2408486168490995</v>
+        <v>-0.1409405808304243</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3959391740605156</v>
+        <v>0.5196357950887602</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.229030956361271</v>
+        <v>-1.080341408583443</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8039336095277818</v>
+        <v>0.9759323690944441</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.06216</t>
+          <t>X ≈ 0.0622</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>140</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.377816409312473</v>
+        <v>-3.379003195757129</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.344016365496074</v>
+        <v>-2.344169755500396</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.6423626504791</v>
+        <v>-3.642857142857103</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6092236321462678</v>
+        <v>-0.560677712380496</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.026135316796854</v>
+        <v>-6.002177907847241</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3177257525083235</v>
+        <v>0.3657374314986441</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5649428230073426</v>
+        <v>0.6141903854010593</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.654041870154792</v>
+        <v>4.753389195449365</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.020769283323162</v>
+        <v>3.120677319341837</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.912290292821268</v>
+        <v>6.035986913849513</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4921394395077741</v>
+        <v>0.6408289872856017</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.1464465183059</v>
+        <v>2.318445277872563</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.07344</t>
+          <t>X ≈ 0.07345</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>136</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6601853151761929</v>
+        <v>0.6600319251718716</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.05511634111748975</v>
+        <v>0.05462184873948672</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.953761447272313</v>
+        <v>-1.905215527506542</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.284789052950963</v>
+        <v>1.308746461900576</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>1.248090372675158</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.468304167545156</v>
+        <v>1.517551729938873</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.06326622427173589</v>
+        <v>0.009990885507960456</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1778909029545375</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3825920612146874</v>
+        <v>-0.2826840251960121</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.122374326434752</v>
+        <v>1.246070947462997</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.437517590768365</v>
+        <v>1.586207138546193</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.663253240994898</v>
+        <v>1.83525200056156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.08471</t>
+          <t>X ≈ 0.0847</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>96</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.894083969465647</v>
+        <v>6.864888175113016</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.449564543068547</v>
+        <v>9.448377756623891</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.971459824980116</v>
+        <v>6.971306434975794</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.976684968568414</v>
+        <v>3.976190476190411</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.563395415472719</v>
+        <v>6.611941335238491</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6107694451078061</v>
+        <v>0.6347268540574191</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.60939241917503</v>
+        <v>2.657404098165351</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.267323775388235</v>
+        <v>5.316571337781951</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.248008285532244</v>
+        <v>6.32126539531194</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.398089489202327</v>
+        <v>5.497436814496901</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.360054997608742</v>
+        <v>9.459963033627417</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.227766483297394</v>
+        <v>5.351463104325639</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.932615629984056</v>
+        <v>8.081305177761884</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.200017946877303</v>
+        <v>9.372016706443965</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.09597</t>
+          <t>X ≈ 0.09596</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>92</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>15.99734483903089</v>
+        <v>15.96814904467826</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.29920222422784</v>
+        <v>13.29801543778319</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>16.16530040469026</v>
+        <v>16.16514701468594</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.86074293958297</v>
+        <v>10.86024844720497</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.800714256052551</v>
+        <v>3.849260175818323</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9.532870894383294</v>
+        <v>9.556828303332907</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.361204013377936</v>
+        <v>8.409215692368257</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.981091891330387</v>
+        <v>9.030339453724103</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.00706625654661</v>
+        <v>10.0803233663263</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.983234416738561</v>
+        <v>7.082581742033135</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.517663693260971</v>
+        <v>3.617571729279646</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.899867932572811</v>
+        <v>8.023564553601055</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.392760557520333</v>
+        <v>6.541450105298161</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.270670120790228</v>
+        <v>2.442668880356891</v>
       </c>
     </row>
     <row r="28">
@@ -1719,358 +1719,358 @@
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.283789851818547</v>
+        <v>9.254594057465916</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.143191994048877</v>
+        <v>9.142005207604221</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>11.68959707988207</v>
+        <v>11.68944368987775</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>11.81982222347043</v>
+        <v>11.81932773109243</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.810944435080621</v>
+        <v>9.859490354846393</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.167141994127476</v>
+        <v>7.191099403077089</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.43537281133189</v>
+        <v>14.48338449032221</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>15.43889240283924</v>
+        <v>15.48813996523295</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>18.31908671690474</v>
+        <v>18.39234382668443</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>17.46916792057492</v>
+        <v>17.56851524586949</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>12.85270205643232</v>
+        <v>12.952610092451</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.475315502905296</v>
+        <v>8.599012123933541</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.99634112018003</v>
+        <v>11.14503066795786</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.751488535112536</v>
+        <v>9.923487294679198</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1185</t>
+          <t>X ≈ 0.1184</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>64</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.894083969465647</v>
+        <v>6.864888175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.092102123598224</v>
+        <v>-4.09328891004288</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.013126491646823</v>
+        <v>8.012973101642501</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.73006208213945</v>
+        <v>10.77860800190522</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.817725752508323</v>
+        <v>7.865737431498644</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.47565710872163</v>
+        <v>10.52490467111534</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.852174952198851</v>
+        <v>8.925432061978547</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.439756155868949</v>
+        <v>6.539103481163522</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.797554997608799</v>
+        <v>7.897463033627474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.394433149964122</v>
+        <v>9.518129770992367</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.849282296650671</v>
+        <v>5.997971844428498</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.075017946877203</v>
+        <v>6.247016706443866</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1298</t>
+          <t>X ≈ 0.1297</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>35</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7.519083969465612</v>
+        <v>7.489888175112981</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.765040733544751</v>
+        <v>8.763853947100095</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.370269348789591</v>
+        <v>8.37011595878527</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.500494492377996</v>
+        <v>8.499999999999993</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.962204939282302</v>
+        <v>8.010750859048073</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.68815039748883</v>
+        <v>19.71210780643844</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.60344003822273</v>
+        <v>19.65145171721305</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>16.27922853729313</v>
+        <v>16.32847609968685</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>19.07538923791321</v>
+        <v>19.14864634769291</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>21.08261329872614</v>
+        <v>21.18196062402072</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.87791214046602</v>
+        <v>20.9778201764847</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>18.05514743567841</v>
+        <v>18.17884405670666</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.77785372522214</v>
+        <v>14.92654327299997</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.71787508973447</v>
+        <v>20.88987384930113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1411</t>
+          <t>X ≈ 0.141</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.280988731370449</v>
+        <v>1.148424760478903</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.19361216211614</v>
+        <v>9.321345236298626</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>14.56074553926579</v>
+        <v>13.80565602847169</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>19.45287544475892</v>
+        <v>18.81358885017421</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.53363351071088</v>
+        <v>15.88531531897839</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.83100754034596</v>
+        <v>16.15810083779732</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>16.09744474857186</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.89827615634068</v>
+        <v>13.19258759794462</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.075389237913058</v>
+        <v>8.277566208319946</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.98737520348804</v>
+        <v>12.33178640799279</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.4017216642754</v>
+        <v>12.12764596045663</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.81705219758313</v>
+        <v>12.18581269782167</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.39690134426982</v>
+        <v>11.79065477125791</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.00358937544868</v>
+        <v>14.47872402351708</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1523</t>
+          <t>X ≈ 0.1522</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.832267381885742</v>
+        <v>-2.510111824887019</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-5.443453474949528</v>
+        <v>-4.093288910042801</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4328194542991639</v>
+        <v>0.7761309963793082</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.4001083919919</v>
+        <v>3.537593984962356</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.861818838896205</v>
+        <v>3.048344844010487</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.861895571233994</v>
+        <v>5.952709310197832</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.330922896140287</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.310116568181087</v>
+        <v>5.426220460589029</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.249134411658311</v>
+        <v>5.389247851452232</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6965129126257494</v>
+        <v>1.933840323268861</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.89721715977096</v>
+        <v>4.361278823101188</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.931595312126326</v>
+        <v>7.051024507834434</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.511444458812875</v>
+        <v>6.655866581270608</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.034477406336705</v>
+        <v>4.273332495917593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.1636</t>
+          <t>X ≈ 0.1634</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.093819256340758</v>
+        <v>-4.12301505069339</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.42402690865981</v>
+        <v>10.42284012221516</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.707867764267448</v>
+        <v>3.707373271889445</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.395384662784586</v>
+        <v>6.443930582550358</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.692758692419673</v>
+        <v>6.716716101369286</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16.28546768799224</v>
+        <v>16.33347936698256</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.140979689366809</v>
+        <v>6.190227251760525</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.53161043606981</v>
+        <v>12.60486754584951</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.68169163973995</v>
+        <v>11.78103896503453</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.47699048147972</v>
+        <v>11.57689851749839</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.51136863383508</v>
+        <v>11.63506525486333</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.54283068374748</v>
+        <v>17.69152023152531</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>17.76856633397397</v>
+        <v>17.94056509354063</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.1749</t>
+          <t>X ≈ 0.1747</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>24</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.18575063613235</v>
+        <v>14.15655484177972</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.092102123598146</v>
+        <v>-4.093288910042801</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.47668496856848</v>
+        <v>16.47619047619048</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.7282712511938527</v>
+        <v>-0.6797253314280809</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.59756388822543</v>
+        <v>-4.573606479275817</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.350657108721592</v>
+        <v>7.399904671115308</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.289674952198851</v>
+        <v>7.362932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.539103481163565</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.235054997608884</v>
+        <v>6.33496303362756</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.60276648329748</v>
+        <v>14.72646310432572</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.18261562998407</v>
+        <v>14.3313051777619</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.4083512802106</v>
+        <v>14.58035003977727</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1041 +2210,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1463</t>
+          <t>X &gt; -0.146</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.3197438693621848</v>
+        <v>-0.3181975530896182</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1106658754301364</v>
+        <v>-0.1103412851950907</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2234970118958515</v>
+        <v>-0.2228943447513032</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2266385895937972</v>
+        <v>-0.226019289021977</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1650430266359137</v>
+        <v>-0.1657484096013633</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.04988662661177301</v>
+        <v>-0.05031947610589071</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.07234516947745107</v>
+        <v>-0.07328695874521429</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.08574210849950958</v>
+        <v>-0.08667742207811813</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01091227559660268</v>
+        <v>-0.01261698633770436</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.01521202817408351</v>
+        <v>-0.01752331893406733</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.03860456921222521</v>
+        <v>0.03613490862747426</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01331170040486285</v>
+        <v>0.0103458882084837</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.04778829714054922</v>
+        <v>0.04413696411589285</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.04243587926333703</v>
+        <v>0.03824563388099733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1351</t>
+          <t>X &gt; -0.1347</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4067</v>
+        <v>4077</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2995434815147391</v>
+        <v>-0.3096228273319639</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08376674728044975</v>
+        <v>-0.07030040429570761</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2445978830466942</v>
+        <v>-0.2306668200796551</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2237074768570793</v>
+        <v>-0.209846551784409</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2089712839056972</v>
+        <v>-0.2208413373018274</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.06995652626227411</v>
+        <v>-0.08156241562836186</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.01855308892511687</v>
+        <v>-0.03093249994108049</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.03026604374583997</v>
+        <v>-0.04253961005046136</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.04507770269000844</v>
+        <v>0.03196684884773759</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.04390747004241291</v>
+        <v>0.0302821138516336</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.07412133667513388</v>
+        <v>0.06045322970590661</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.02404116176063553</v>
+        <v>0.03434085213969951</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.06019675092800014</v>
+        <v>0.04529896556635293</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.0294069313867098</v>
+        <v>0.01387959582335441</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1238</t>
+          <t>X &gt; -0.1235</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3241499472215637</v>
+        <v>-0.3094725330256551</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1473289480557796</v>
+        <v>-0.13362339110531</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3561706723482914</v>
+        <v>-0.3418854469430244</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3359280884945051</v>
+        <v>-0.3217097862767133</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2934081867971372</v>
+        <v>-0.2808000709473504</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.08127563551075667</v>
+        <v>-0.06843661221528663</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.004416928311187007</v>
+        <v>0.007451295079086151</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01354042214257589</v>
+        <v>-0.001573161396969169</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.06258184278912182</v>
+        <v>0.07357507749961201</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.01683125468322544</v>
+        <v>0.02727499422419299</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.02366384366760599</v>
+        <v>0.03412497594938912</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.02690891627413805</v>
+        <v>-0.0171266392640419</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.01289322868921516</v>
+        <v>-0.003877724005498351</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06988808675282598</v>
+        <v>-0.0615674080109514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1125</t>
+          <t>X &gt; -0.1122</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4008</v>
+        <v>4019</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3297098629143633</v>
+        <v>-0.3275721423473001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2363807305633543</v>
+        <v>-0.2356853377282775</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4684609679202723</v>
+        <v>-0.4671757817322373</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4492317395782024</v>
+        <v>-0.4479842569939407</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4264290804196733</v>
+        <v>-0.427325463834606</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1652929718908069</v>
+        <v>-0.1658587762711363</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1119131017880193</v>
+        <v>-0.1136465724754814</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.141869049723816</v>
+        <v>-0.1435735897542187</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01020821908148406</v>
+        <v>0.007067250845338435</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.07819000564646217</v>
+        <v>-0.0821990294006909</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.01961964711819775</v>
+        <v>-0.02381369436854186</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1208411642503364</v>
+        <v>-0.1257709999601317</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1029501802761956</v>
+        <v>-0.1089933297008088</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.162507003222558</v>
+        <v>-0.1693804072659759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1013</t>
+          <t>X &gt; -0.101</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3956</v>
+        <v>3965</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4023068090679871</v>
+        <v>-0.3984979485672184</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2362553494046296</v>
+        <v>-0.2335956739352198</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4409950107479688</v>
+        <v>-0.4125802182770641</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4484284958793268</v>
+        <v>-0.445193171608274</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3678256858302902</v>
+        <v>-0.3672777555180247</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2080583382759187</v>
+        <v>-0.2066293838819462</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1276439169339696</v>
+        <v>-0.1277167477561036</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1266270911774114</v>
+        <v>-0.1265370312266327</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.07874336926525416</v>
+        <v>0.07703785542943109</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02561474172757272</v>
+        <v>0.0229785126576445</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1129281979119057</v>
+        <v>0.1101646465306985</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.06583718859069876</v>
+        <v>-0.06956243974622822</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.04217587873467465</v>
+        <v>-0.047161791476654</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05491127455854894</v>
+        <v>-0.06130611827236265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.08998</t>
+          <t>X &gt; -0.0897</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3901</v>
+        <v>3910</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4880698373815662</v>
+        <v>-0.4836015011551495</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2715041169536647</v>
+        <v>-0.2942068090739411</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.4480187026272517</v>
+        <v>-0.4701944576536405</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4318209548952581</v>
+        <v>-0.4540816326530575</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4703854881930383</v>
+        <v>-0.4957923553287742</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1846705651249252</v>
+        <v>-0.2091348100568595</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.07633770706174658</v>
+        <v>-0.07720359479694849</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.0175281996991572</v>
+        <v>-0.01837929211243505</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.08921412270576923</v>
+        <v>0.06088863924547638</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1241351571493965</v>
+        <v>0.09428999112779479</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2668172926907673</v>
+        <v>0.2367008307141134</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1107090915475268</v>
+        <v>0.1047862127101595</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.191927094190433</v>
+        <v>0.1842413407210515</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1502550655647639</v>
+        <v>0.1153031514566933</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07871</t>
+          <t>X &gt; -0.07845</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3818</v>
+        <v>3827</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4057398363291895</v>
+        <v>-0.3746951582203195</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2017626980107181</v>
+        <v>-0.172997167401526</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5302268643208379</v>
+        <v>-0.5266308587535775</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5687695768860763</v>
+        <v>-0.5651178375963397</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5965318556708468</v>
+        <v>-0.5971740627454523</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2849658746342456</v>
+        <v>-0.2841671050907166</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1463265350733352</v>
+        <v>-0.1480862513390733</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.04997050634113265</v>
+        <v>-0.02574103720711207</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.01806765831644697</v>
+        <v>0.003850642354336742</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1668623829752178</v>
+        <v>0.1863235281486908</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3694439010372221</v>
+        <v>0.3884878378050232</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2092237258803493</v>
+        <v>0.2002595698954792</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3013639934299803</v>
+        <v>0.2900303606249821</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3062908646352369</v>
+        <v>0.2926137798695621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06744</t>
+          <t>X &gt; -0.0672</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3723</v>
+        <v>3730</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6340209555878857</v>
+        <v>-0.5998793910104183</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3571623645620292</v>
+        <v>-0.3519741051256773</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6036383717704652</v>
+        <v>-0.5976924957913852</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.619707566479299</v>
+        <v>-0.5870893812070292</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5541019049988165</v>
+        <v>-0.5270552770463723</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3225705888419199</v>
+        <v>-0.2932426483502297</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1782527997704477</v>
+        <v>-0.1520575912468374</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.06755152630116612</v>
+        <v>-0.04120881924868058</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.07400971614734431</v>
+        <v>0.09720247697185158</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3658361129390215</v>
+        <v>0.3861843595781309</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4983400217633829</v>
+        <v>0.5185955008120473</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3331915392258651</v>
+        <v>0.3775885062549662</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3847280539009859</v>
+        <v>0.3728043290171215</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3840429267322065</v>
+        <v>0.395810272127548</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05617</t>
+          <t>X &gt; -0.05595</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3616</v>
+        <v>3624</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5382320955660376</v>
+        <v>-0.5299138050850019</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3159168975783331</v>
+        <v>-0.3106204093550815</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4201516996959285</v>
+        <v>-0.3593439044114746</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.302594310710802</v>
+        <v>-0.2696118909991796</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3570068833777995</v>
+        <v>-0.3309734958921382</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.09977139374423416</v>
+        <v>-0.09825533634001715</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.00383096844112174</v>
+        <v>-0.006163394947591883</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2344229839286953</v>
+        <v>0.2319520670922017</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3820527483877498</v>
+        <v>0.3756112240513119</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5972147194049029</v>
+        <v>0.5872148679846276</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6568566002614631</v>
+        <v>0.658784373577852</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.485851060411882</v>
+        <v>0.4844149337060983</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4684418211185033</v>
+        <v>0.4634890858078577</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4334250265232669</v>
+        <v>0.4523147196889425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.0449</t>
+          <t>X &gt; -0.0447</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3454</v>
+        <v>3462</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4186143287749005</v>
+        <v>-0.3913456098394192</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1971223197897487</v>
+        <v>-0.2005553460289988</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4031794246591431</v>
+        <v>-0.4345319459491179</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4305513670743295</v>
+        <v>-0.4910147555848638</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5201183972137216</v>
+        <v>-0.560677712380496</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1781531429914978</v>
+        <v>-0.2301721358415136</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.04488620935237009</v>
+        <v>-0.1019300049909262</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2552813861782752</v>
+        <v>0.1828146018312822</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2392268458097249</v>
+        <v>0.1747103529716227</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5042442993045029</v>
+        <v>0.4767478229649527</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6341004127086052</v>
+        <v>0.5901593384773633</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.540266483297458</v>
+        <v>0.5328526347337075</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.57070053109355</v>
+        <v>0.5005707471140752</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4655796145089823</v>
+        <v>0.4483454181712361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03363</t>
+          <t>X &gt; -0.03344</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3251</v>
+        <v>3258</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3203276149658549</v>
+        <v>-0.2895911510738074</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1068170224332547</v>
+        <v>-0.07980851788597221</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3317063817049544</v>
+        <v>-0.3344066102790819</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2768937635378634</v>
+        <v>-0.2798896382587372</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5224310139022776</v>
+        <v>-0.5378976712011934</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.116287031258004</v>
+        <v>-0.1424503921860065</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.214870364114141</v>
+        <v>0.2123631983698573</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4403376984022174</v>
+        <v>0.3907022171276182</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4271557509699733</v>
+        <v>0.3844044546165861</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7006658055309387</v>
+        <v>0.6648703523292028</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8823036911224733</v>
+        <v>0.8595029109280929</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.903504490677534</v>
+        <v>0.8869948016672211</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.023843969981996</v>
+        <v>0.9695889048765309</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7881831268218846</v>
+        <v>0.7758687629202754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02236</t>
+          <t>X &gt; -0.02219</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3027</v>
+        <v>3033</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4400997040037353</v>
+        <v>-0.4363791059929767</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.02558911734200109</v>
+        <v>0.03907855785310943</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2707997270620481</v>
+        <v>-0.2380150406500334</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1556598968900715</v>
+        <v>-0.1891033184278683</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3464870279462531</v>
+        <v>-0.3488631677817651</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1337252644286764</v>
+        <v>0.0886669968361673</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3968814253315855</v>
+        <v>0.3575001992087365</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7068101935121192</v>
+        <v>0.6494928095008419</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7962756122648571</v>
+        <v>0.7443159170032629</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.054315416351002</v>
+        <v>1.007801998461751</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.000576794174187</v>
+        <v>0.968406196724672</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.053873189607337</v>
+        <v>1.026572934089565</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9971184380448292</v>
+        <v>0.9798439604470062</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8264219772703711</v>
+        <v>0.8521930994541336</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01109</t>
+          <t>X &gt; -0.01094</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1947803373190098</v>
+        <v>-0.08867005039530085</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2220571684372175</v>
+        <v>0.3075986639216595</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1055278195700566</v>
+        <v>0.2299542337179261</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.002404822329438616</v>
+        <v>0.08401184307919607</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1145761607546092</v>
+        <v>0.001868549647632278</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1660993318631583</v>
+        <v>0.2376444459647118</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.507973258973081</v>
+        <v>0.5470845817577512</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.9112631693276825</v>
+        <v>0.9324731389169685</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.018880127799591</v>
+        <v>0.9695197747838833</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.373188108531707</v>
+        <v>1.329999114028112</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.226730913258073</v>
+        <v>1.088849043990173</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.54145387535273</v>
+        <v>1.443092761369869</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.454389624555972</v>
+        <v>1.381021437322694</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.236009804760293</v>
+        <v>1.244239957091821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001758</t>
+          <t>X &gt; 0.0003112</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.473228590276932</v>
+        <v>0.5141707358194196</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7138943490649652</v>
+        <v>0.8095379450808409</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4756320055417902</v>
+        <v>0.4400610380101142</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.0324120675245112</v>
+        <v>0.06372363268914683</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2170914924413125</v>
+        <v>-0.1602735188728559</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4934156093199036</v>
+        <v>-0.5064093086304098</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.569270324441284</v>
+        <v>0.5823598895004523</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8771471749467921</v>
+        <v>0.8680744323885534</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.061759757852563</v>
+        <v>1.096353812641674</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.56238099015976</v>
+        <v>1.598785178776296</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.73682334420473</v>
+        <v>1.748314050426771</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.257496810441573</v>
+        <v>2.248567436774863</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.881554622026492</v>
+        <v>1.897618175109351</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.974664277558055</v>
+        <v>2.039807506974647</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.01145</t>
+          <t>X &gt; 0.01156</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1873</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7423125256723608</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.42201615024306</v>
+        <v>1.509699350362716</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6543092300591411</v>
+        <v>0.6651354081026852</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.157469909076383</v>
+        <v>1.168751430096854</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6191803559806885</v>
+        <v>0.6261120061764487</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4370658400643563</v>
+        <v>0.3649946953103722</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.098226551655948</v>
+        <v>1.105192850612411</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.03402597865766</v>
+        <v>1.013092071008558</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.429674952198852</v>
+        <v>1.403241725619765</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.370919442955433</v>
+        <v>2.341292482765276</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.464366262958507</v>
+        <v>2.404103450071688</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.765695830156325</v>
+        <v>2.729221602279075</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.292154693874416</v>
+        <v>2.280673392746749</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.411109778163954</v>
+        <v>2.422937688825108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02272</t>
+          <t>X &gt; 0.02282</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9571979183850985</v>
+        <v>1.02855134680371</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.50711202178492</v>
+        <v>1.578842237498144</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3264860201340056</v>
+        <v>0.3982190032818025</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1947596247570829</v>
+        <v>0.2002341920374704</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2780420435972886</v>
+        <v>-0.1578674079308442</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1771316681861705</v>
+        <v>-0.08180320058733059</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5895004741848595</v>
+        <v>0.6444259560888526</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.235725871000604</v>
+        <v>1.293347294066159</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.735939696628741</v>
+        <v>1.780964848863789</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.300411893573909</v>
+        <v>2.33418544837668</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.330855522543182</v>
+        <v>2.326766312315996</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.890168058100606</v>
+        <v>2.909523213615316</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.601250800587714</v>
+        <v>2.645512828035102</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.564519259213206</v>
+        <v>2.632262608083259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.03399</t>
+          <t>X &gt; 0.03407</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1240</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.027940652235372</v>
+        <v>2.086662368661408</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.543968729863977</v>
+        <v>1.632517541570067</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8271361534825274</v>
+        <v>0.8355537468037468</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6353001054444789</v>
+        <v>0.6428571428571459</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3385564460685941</v>
+        <v>0.3955434857761801</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.635930475703681</v>
+        <v>0.6683290045951082</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.000495478756349</v>
+        <v>2.059285818595455</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.580125707755442</v>
+        <v>2.641840154986312</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.210303477581604</v>
+        <v>3.250028836172092</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.052659381675447</v>
+        <v>3.071361545679693</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.573764675028151</v>
+        <v>3.593027549756499</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.092013795125418</v>
+        <v>4.135065254863335</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.591217780521681</v>
+        <v>3.659262167009182</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.413727624296598</v>
+        <v>3.505081222572933</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.04526</t>
+          <t>X &gt; 0.04532</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1015</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.381152934982886</v>
+        <v>3.351957140630255</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.247799354234331</v>
+        <v>3.246612567789676</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.050072304454666</v>
+        <v>3.049918914450345</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.490642275629227</v>
+        <v>2.490147783251224</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.656786220070487</v>
+        <v>1.705332139836258</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.15120458468094</v>
+        <v>2.175161993630553</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.741371072705412</v>
+        <v>3.789382751695733</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.653612773746254</v>
+        <v>4.70286033613997</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.986719287174218</v>
+        <v>5.059976396953914</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.220544333208899</v>
+        <v>5.319891658503472</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.606976179874806</v>
+        <v>5.706884215893481</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.331009504643923</v>
+        <v>6.454706125672168</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.418247813892094</v>
+        <v>5.566937361669922</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.742505631606306</v>
+        <v>5.914504391172969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.05653</t>
+          <t>X &gt; 0.05657</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>849</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.87833014143267</v>
+        <v>2.849134347080039</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.093999172043752</v>
+        <v>4.092812385599096</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.99486971897305</v>
+        <v>4.994716328968728</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.653952341948923</v>
+        <v>4.65345784957092</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.644520268240747</v>
+        <v>3.693066188006519</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.470751777263345</v>
+        <v>3.494709186212958</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.623968390906477</v>
+        <v>5.671980069896797</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.216970418497837</v>
+        <v>6.266217980891554</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.744916412740665</v>
+        <v>6.818173522520361</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.71949702748266</v>
+        <v>6.818844352777234</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.750367129528712</v>
+        <v>6.850275165547387</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.491459062802754</v>
+        <v>7.615155683830999</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.717951319029979</v>
+        <v>6.866640866807806</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.708115708950281</v>
+        <v>6.880114468516943</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0678</t>
+          <t>X &gt; 0.06782</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>709</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.641792008957893</v>
+        <v>4.612596214605261</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.569392939871491</v>
+        <v>5.568206153426836</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.444015067105177</v>
+        <v>6.443861677100855</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.292152763584923</v>
+        <v>6.29165827120692</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.484469698500519</v>
+        <v>4.53301561826629</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.346018622352808</v>
+        <v>5.369976031302421</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.671745498629669</v>
+        <v>6.719757177619989</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.333026643277343</v>
+        <v>7.38227420567106</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.695175657417472</v>
+        <v>7.768432767197169</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.127344308196214</v>
+        <v>7.226691633490788</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.486818044153232</v>
+        <v>7.586726080171907</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.803283643617156</v>
+        <v>7.926980264645401</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.94730768452095</v>
+        <v>8.095997232298778</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.60886844053028</v>
+        <v>7.780867200096942</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>573</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.634267215538948</v>
+        <v>5.605071421186317</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.768281820555394</v>
+        <v>5.767095034110739</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.816791413112753</v>
+        <v>7.816638023108432</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.772496486893075</v>
+        <v>7.772001994515072</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.012566445141189</v>
+        <v>6.061112364906961</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.309940474776276</v>
+        <v>6.333897883725889</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.97043081359039</v>
+        <v>8.018442492580711</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.72500265845985</v>
+        <v>8.774250220853567</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>9.536620850977215</v>
+        <v>9.609877960756911</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.861222124455381</v>
+        <v>8.960569449749954</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.35460124542729</v>
+        <v>9.454509281445965</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.388979397782613</v>
+        <v>9.512676018810858</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.492388753893295</v>
+        <v>9.641078301671122</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.020044124887711</v>
+        <v>9.192042884454374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.09034</t>
+          <t>X &gt; 0.09033</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>477</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.380719189591431</v>
+        <v>5.3515233952388</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.027394731747727</v>
+        <v>5.026207945303071</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.986921040913025</v>
+        <v>7.986767650908703</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.536433396241428</v>
+        <v>8.535938903863425</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.901707784445534</v>
+        <v>5.950253704211306</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.456943449300745</v>
+        <v>7.480900858250358</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.049381936994742</v>
+        <v>9.097393615985062</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.420887716688092</v>
+        <v>9.470135279081809</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.19847998364538</v>
+        <v>10.27173709342508</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.558204793185553</v>
+        <v>9.657552118480126</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.35350363492536</v>
+        <v>9.453411670944035</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.22645621076077</v>
+        <v>10.35015283178901</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.806305357447357</v>
+        <v>9.954994905225185</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.983822978323779</v>
+        <v>9.155821737890442</v>
       </c>
     </row>
     <row r="28">
@@ -3361,98 +3361,98 @@
         <v>385</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.843759294140966</v>
+        <v>2.814563499788335</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.032607011127297</v>
+        <v>6.032453621122976</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.981013972897479</v>
+        <v>7.980519480519476</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.403763380840743</v>
+        <v>6.452309300606515</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.960877670216092</v>
+        <v>6.984835079165705</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.213829648612261</v>
+        <v>9.261841327602582</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.525981784046301</v>
+        <v>9.575229346440018</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.2442204067443</v>
+        <v>10.317477516524</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.17352238963522</v>
+        <v>10.2728697149298</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.74804201059581</v>
+        <v>10.84795004661449</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.78242016295113</v>
+        <v>10.90611678397938</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.62200956937798</v>
+        <v>10.77069911715581</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.58800495986426</v>
+        <v>10.76000371943092</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1129</t>
+          <t>X &gt; 0.1128</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.462301635080784</v>
+        <v>1.433105840728153</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.743860021512226</v>
+        <v>1.742673235067571</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.819120182498516</v>
+        <v>4.818966792494194</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.157547218831354</v>
+        <v>7.157052726453351</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.672885425988028</v>
+        <v>5.7214313457538</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.916631695370747</v>
+        <v>6.94058910432036</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.093750989101423</v>
+        <v>8.141762668091744</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.257597171813117</v>
+        <v>8.306844734206834</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.512072428539547</v>
+        <v>8.585329538319243</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.608525871957312</v>
+        <v>8.707873197251885</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.2965691931924</v>
+        <v>10.39647722921107</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.27731958529535</v>
+        <v>11.4010162063236</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.54171131873274</v>
+        <v>10.69040086651056</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.76744696895927</v>
+        <v>10.93944572852593</v>
       </c>
     </row>
     <row r="30">
@@ -3465,306 +3465,306 @@
         <v>253</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.08825392993995251</v>
+        <v>0.0590581355873212</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.220150840828701</v>
+        <v>3.218964054384045</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.011150207061796</v>
+        <v>4.010996817057475</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.908173769622493</v>
+        <v>6.90767927724449</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.393599631546564</v>
+        <v>4.442145551312336</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.667258246161886</v>
+        <v>6.691215655111499</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.163575554879912</v>
+        <v>8.211587233870233</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.696506911093174</v>
+        <v>7.74575447348689</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>8.499295698342181</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.157147460216819</v>
+        <v>9.256494785511393</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.92873088693686</v>
+        <v>11.02863892295554</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.75362287328428</v>
+        <v>11.87731949431252</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.72872893696693</v>
+        <v>11.87741848474476</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.95446458719346</v>
+        <v>12.12646334676013</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1354</t>
+          <t>X &gt; 0.1353</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>218</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.104769241543522</v>
+        <v>-1.133965035896153</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.32991622502567</v>
+        <v>2.328729438581014</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.311291629261454</v>
+        <v>3.311138239257133</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.652525947161749</v>
+        <v>6.652031454783746</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.82065841241468</v>
+        <v>3.869204332180452</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.576748038380039</v>
+        <v>4.600705447329652</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.326900064434973</v>
+        <v>6.374911743425294</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.318547016978506</v>
+        <v>6.367794579372223</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.716280456786002</v>
+        <v>6.789537566565699</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.242508449446973</v>
+        <v>7.341855774741546</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.331385272838148</v>
+        <v>9.431293308856823</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.74191021418431</v>
+        <v>10.86560683521255</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.23919055353146</v>
+        <v>11.38788010130929</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.54749501109743</v>
+        <v>10.71949377066409</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1467</t>
+          <t>X &gt; 0.1466</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.912734212352532</v>
+        <v>-1.66265419776834</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.7089709769628101</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6267628552831468</v>
+        <v>0.8802047400605346</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.597897089780602</v>
+        <v>3.83494753833736</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.7868802639576273</v>
+        <v>1.085811391735724</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.652436111774534</v>
+        <v>1.923568661967089</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.840453025235639</v>
+        <v>4.122799578391344</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.509748017812534</v>
+        <v>4.78691032083286</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.153311315835218</v>
+        <v>6.44485296593335</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.871574337687171</v>
+        <v>6.185996136530804</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.075964088517892</v>
+        <v>8.806714446056858</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.24670587723686</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.96291866028707</v>
+        <v>11.29458201392006</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.484108855968152</v>
+        <v>9.848711621698151</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.158</t>
+          <t>X &gt; 0.1578</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>139</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.401779339886865</v>
+        <v>-1.430975134239496</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.023005790070876</v>
+        <v>2.02181900362622</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.9088099448841902</v>
+        <v>0.9086565548798688</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.916732930199174</v>
+        <v>3.916238437821171</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5007455353768577</v>
+        <v>0.5492914551426296</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7981195650119446</v>
+        <v>0.8220769739615577</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.74938042876736</v>
+        <v>5.79739210775768</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.56288732454896</v>
+        <v>4.612134886942677</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.660178549321159</v>
+        <v>6.733435659100856</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.2491086738546</v>
+        <v>7.348455999149174</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.92210535732103</v>
+        <v>10.02201339333971</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.39533243053966</v>
+        <v>11.51902905156791</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.41403049808956</v>
+        <v>12.56272004586739</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.20091722745278</v>
+        <v>11.37291598701945</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1692</t>
+          <t>X &gt; 0.1691</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>108</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.6290641786825049</v>
+        <v>-0.6582599730351362</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3883984198944717</v>
+        <v>-0.3895852063391274</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.191234214156843</v>
+        <v>-1.142688294391071</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.8938601845217562</v>
+        <v>-0.8699027755721431</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.725133159915771</v>
+        <v>2.773144838906092</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.10991636798088</v>
+        <v>4.159163930374596</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.974860137384034</v>
+        <v>5.048117247163731</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.97679319290603</v>
+        <v>6.076140518200603</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.475795738349547</v>
+        <v>9.575703774368222</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.36202574255672</v>
+        <v>11.48572236358496</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.94187488924331</v>
+        <v>11.09056443702114</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.315758687617993</v>
+        <v>9.487757447184656</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.1805</t>
+          <t>X &gt; 0.1803</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.861868411486739</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1041 +3904,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1463</t>
+          <t>X &lt; -0.146</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.5667030170847</v>
+        <v>16.53750722273207</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.3840883525923</v>
+        <v>11.38290156614764</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.56074553926583</v>
+        <v>14.56059214926151</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15.88144687333037</v>
+        <v>15.88095238095237</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.96220493928231</v>
+        <v>13.01075085904808</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.497674207012629</v>
+        <v>8.521631615962242</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.79391622869885</v>
+        <v>10.84192790768917</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.32684758491211</v>
+        <v>10.37609514730583</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.225470441583283</v>
+        <v>8.324817766877857</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>6.988367866230462</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.289303661162954</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1351</t>
+          <t>X &lt; -0.1347</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.17564962603131</v>
+        <v>13.48988817511302</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.534160502664449</v>
+        <v>7.906711089957163</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.18989416841446</v>
+        <v>12.51297310164246</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.32011931200282</v>
+        <v>12.64285714285714</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.78182975890713</v>
+        <v>13.15360800190522</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.028698738037164</v>
+        <v>8.426393520724147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.933887368669978</v>
+        <v>7.365737431498687</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.46681872488324</v>
+        <v>6.899904671115344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.385634548158443</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.545816761929601</v>
+        <v>5.039103481163565</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.331014593568391</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.385594766125735</v>
+        <v>4.893129770992367</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.955342902711322</v>
+        <v>4.497971844428541</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.181078552937855</v>
+        <v>4.747016706443908</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1238</t>
+          <t>X &lt; -0.1235</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.45351019897385</v>
+        <v>10.90452232145448</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.022651974762475</v>
+        <v>8.508337106217319</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.36558550804022</v>
+        <v>13.80565602847173</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14.49581065162858</v>
+        <v>13.93554006968641</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.13784896738535</v>
+        <v>12.63328279865319</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.877845947840107</v>
+        <v>6.402003276821709</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.153791326278856</v>
+        <v>4.715330927433648</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.686722682492118</v>
+        <v>4.249498167050305</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.986396263674258</v>
+        <v>2.586509297750908</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.595493860787023</v>
+        <v>4.201705107179833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.390792702526831</v>
+        <v>3.997564659643743</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.064515117177237</v>
+        <v>5.681747657171229</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.644364263863828</v>
+        <v>5.286589730607403</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.689772045237902</v>
+        <v>6.348642722704064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1125</t>
+          <t>X &lt; -0.1122</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>158</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.911489032756791</v>
+        <v>8.882293238404159</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.199037116908151</v>
+        <v>9.197850330463496</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.86755687139361</v>
+        <v>13.86740348138929</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13.99778201498197</v>
+        <v>13.99728752260397</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13.45949246188628</v>
+        <v>13.50803838165205</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.427752567470733</v>
+        <v>7.451709976420346</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.710130815799509</v>
+        <v>6.75814249478983</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.875973564417826</v>
+        <v>6.925221126811543</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.650434445869742</v>
+        <v>3.723691555649438</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.965072611565191</v>
+        <v>6.064419936859764</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.494548668494879</v>
+        <v>4.594456704513554</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.060572390470455</v>
+        <v>7.184269011498699</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.640421537157046</v>
+        <v>6.789111084934873</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.499068579788634</v>
+        <v>7.671067339355297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1013</t>
+          <t>X &lt; -0.101</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.995274445656122</v>
+        <v>7.867246665679055</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.860278828782775</v>
+        <v>6.755767693730753</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.192218384661331</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.4052563971399</v>
+        <v>10.2654986522911</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.914585891663251</v>
+        <v>8.832853284924091</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.35481706415549</v>
+        <v>6.275450124497738</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.271397808857181</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.805565048473838</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.456341618865515</v>
+        <v>1.466705646884208</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.511184727297568</v>
+        <v>2.529669518899411</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9104347317406862</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.245623626154597</v>
+        <v>4.270488261558405</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.825472772841188</v>
+        <v>3.87533033499458</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.652677083802402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.08998</t>
+          <t>X &lt; -0.0897</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.414981808071822</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>6.206336558121961</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.777277435043004</v>
+        <v>8.059789581043205</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.907502578631366</v>
+        <v>8.189673622257885</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.501288497233787</v>
+        <v>8.824019986923943</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.647719130642457</v>
+        <v>4.976955318476961</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.430933299678173</v>
+        <v>3.418171888427523</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.209147674759365</v>
+        <v>2.203275457632195</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.016090046538473</v>
+        <v>1.41723917808342</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5435297407746518</v>
+        <v>0.9679424324744232</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.547963870315733</v>
+        <v>-1.108857191091623</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.750565225435821</v>
+        <v>0.8219687223032253</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4243026090096649</v>
+        <v>-0.3222528746725786</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1985669587831325</v>
+        <v>0.3013238225487811</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07871</t>
+          <t>X &lt; -0.07845</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.702992015442668</v>
+        <v>4.347031032255877</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.666518566056993</v>
+        <v>3.335282518528594</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.720023043370915</v>
+        <v>6.655830244499604</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.424960830637438</v>
+        <v>7.357142857142847</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.748740243058982</v>
+        <v>7.725036573333789</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.597838410625108</v>
+        <v>4.569250663581286</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.363702764002618</v>
+        <v>3.36573743149868</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.034565154698647</v>
+        <v>1.757047528258205</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.973582998175871</v>
+        <v>1.720074919121409</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.02576108551032519</v>
+        <v>-0.2466108045507198</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.241956496644072</v>
+        <v>-2.45075125208681</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.4834404132542645</v>
+        <v>-0.3925845147219178</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.478303910245842</v>
+        <v>-1.35917101271432</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.827280903697464</v>
+        <v>-1.681554722127522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06744</t>
+          <t>X &lt; -0.0672</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.532627987524343</v>
+        <v>5.208008980482148</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.147175528772024</v>
+        <v>4.072259188391172</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.784006852820596</v>
+        <v>5.691944018868405</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.139965630720468</v>
+        <v>5.821828060083085</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.601676077624774</v>
+        <v>5.332578919131166</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.86744739845625</v>
+        <v>3.591941619158156</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.879802501944027</v>
+        <v>2.636430943802935</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.735532955222752</v>
+        <v>1.499457243822278</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7716162614539286</v>
+        <v>0.5676300485557277</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.658437975056515</v>
+        <v>-1.82219405798633</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.766073670562754</v>
+        <v>-2.921189091652167</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.377293712338357</v>
+        <v>-1.744454121625083</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.797444565651766</v>
+        <v>-1.692184755124039</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.02317618404826</v>
+        <v>-2.114280832705987</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05617</t>
+          <t>X &lt; -0.05595</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.700902151283827</v>
+        <v>3.627072290636484</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.998806967310912</v>
+        <v>2.946422281292904</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.331308309828593</v>
+        <v>2.913695123303114</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.734260726144235</v>
+        <v>2.502062919030422</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.10506208213944</v>
+        <v>2.915340853890775</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.584254293592714</v>
+        <v>1.563577636247615</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.135907570690186</v>
+        <v>1.141910716697247</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.587459949823284</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.392143229619329</v>
+        <v>-1.346454219609903</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.787516571403735</v>
+        <v>-2.711799045912244</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.174035911482115</v>
+        <v>-3.181311830748655</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.048748668217691</v>
+        <v>-2.03815413497508</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.92344497607656</v>
+        <v>-1.890816582334566</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-2.003435373122095</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.0449</t>
+          <t>X &lt; -0.0447</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.153915430139811</v>
+        <v>1.997516469149076</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.666324842693946</v>
+        <v>1.66260568080321</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.395148963556892</v>
+        <v>2.517133989298486</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.6658235453475</v>
+        <v>2.924410540915389</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.110680059667537</v>
+        <v>3.267338931170123</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.582211392673415</v>
+        <v>1.815282409613033</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.076152718800493</v>
+        <v>1.337959653720908</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5145114306042089</v>
+        <v>-0.1626822551711626</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2945947107224995</v>
+        <v>0.01613540459693041</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.565861821659098</v>
+        <v>-1.428121065558884</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.19191129452603</v>
+        <v>-1.975092832294308</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.736184827563967</v>
+        <v>-1.701275823413226</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.875436804472884</v>
+        <v>-1.536993190536492</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.509251716044105</v>
+        <v>-1.427808468381265</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03363</t>
+          <t>X &lt; -0.03344</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.230874362478751</v>
+        <v>1.111509796734637</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9297319375371842</v>
+        <v>0.8256300088760895</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.517493303873849</v>
+        <v>1.512973101642466</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.429377836108507</v>
+        <v>1.426640926640921</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.310302256811937</v>
+        <v>2.342797191094412</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.9701217012941896</v>
+        <v>1.054099148429771</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.09712140906368205</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.000871275557841</v>
+        <v>-0.8205720352768537</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8435128207269145</v>
+        <v>-0.6902132742470499</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.802601922733629</v>
+        <v>-1.672080015036215</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.443984303701242</v>
+        <v>-2.360689140285572</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.518776457022774</v>
+        <v>-2.461603634883581</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.938927310336183</v>
+        <v>-2.747947633264602</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.217331779898714</v>
+        <v>-2.17246098670082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02236</t>
+          <t>X &lt; -0.02219</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.243886774023053</v>
+        <v>1.222527064001902</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5091248702668452</v>
+        <v>0.3337944232904988</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9907776748194408</v>
+        <v>0.8949175460869014</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7704331426847446</v>
+        <v>0.8511904761904745</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.283852616758196</v>
+        <v>1.278716603121552</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.09130552457033048</v>
+        <v>0.2090022163763194</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5192593482804213</v>
+        <v>-0.4132007756379537</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.424540086720967</v>
+        <v>-1.267342715644233</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.573164662174499</v>
+        <v>-1.431749716574203</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.24779862064284</v>
+        <v>-2.121454983059827</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.101930103179988</v>
+        <v>-2.016565350651994</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.242836788686184</v>
+        <v>-2.173303795441193</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.089314194577355</v>
+        <v>-2.043986197529499</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.727879331437066</v>
+        <v>-1.794941335514132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01109</t>
+          <t>X &lt; -0.01094</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1464</v>
+        <v>1476</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4161528174547371</v>
+        <v>0.2171609023857357</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.06754550695425365</v>
+        <v>-0.2212350379889685</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.01517287636710307</v>
+        <v>-0.2109326222632646</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2818236679772994</v>
+        <v>0.1209716209716163</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4938751790016553</v>
+        <v>0.2749018024443046</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.04090814451669189</v>
+        <v>-0.08945273686182986</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5212919828258791</v>
+        <v>-0.5856795725498927</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.329424746667186</v>
+        <v>-1.352627401808356</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.458619727200876</v>
+        <v>-1.353284154237677</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.103900051498002</v>
+        <v>-2.005521265286738</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.831111441681792</v>
+        <v>-1.564225058388764</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.410648705424691</v>
+        <v>-2.213843824132887</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.247987327922665</v>
+        <v>-2.09823411763108</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.916785331811276</v>
+        <v>-1.916939933122485</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001758</t>
+          <t>X &lt; 0.0003112</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1904</v>
+        <v>1916</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5185926396395359</v>
+        <v>-0.5620598768350433</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5842487204568201</v>
+        <v>-0.690691507445429</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.403103874845371</v>
+        <v>-0.357156768487414</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1745197860994736</v>
+        <v>0.1363636363636331</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4743653822965967</v>
+        <v>0.4030882513854763</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8531698643950776</v>
+        <v>0.8606108894188935</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3561074934276576</v>
+        <v>-0.3678733905616696</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7707377523166485</v>
+        <v>-0.7534008989002672</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9365966786349205</v>
+        <v>-0.9704012713547883</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.524323550476048</v>
+        <v>-1.557561448487299</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.72902470873624</v>
+        <v>-1.733337279198388</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.348090459689601</v>
+        <v>-2.32491926395808</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.900061535370284</v>
+        <v>-1.909126276657055</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.065738355643767</v>
+        <v>-2.129810015894293</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.01145</t>
+          <t>X &lt; 0.01156</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2293</v>
+        <v>2304</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5695346230625873</v>
+        <v>-0.6310621488610622</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9412981253365587</v>
+        <v>-1.004735994276096</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3999169866140946</v>
+        <v>-0.4049534642322783</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7681316183533724</v>
+        <v>-0.7702802815162357</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3257473173383616</v>
+        <v>-0.3284499315145837</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1352217027661737</v>
+        <v>-0.07533658308207691</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.6317515994080125</v>
+        <v>-0.6316662898340653</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6197261665396994</v>
+        <v>-0.5979308267201517</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.898478357905681</v>
+        <v>-0.8711519570773163</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.661289140298251</v>
+        <v>-1.628140886254116</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.735328277652528</v>
+        <v>-1.678691062601402</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.982200836963983</v>
+        <v>-1.943817323543627</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.594048130550689</v>
+        <v>-1.57795006446517</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.736800631404478</v>
+        <v>-1.739094404667206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02272</t>
+          <t>X &lt; 0.02282</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2642</v>
+        <v>2652</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5201317168088551</v>
+        <v>-0.5581598729350361</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6782960126966273</v>
+        <v>-0.7149105316644579</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.0717791687305791</v>
+        <v>-0.1122615960668938</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0412376299501318</v>
+        <v>0.03804872813136484</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3165424446772178</v>
+        <v>0.2456786520367515</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.294767052462106</v>
+        <v>0.238423595912117</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.10933396026563</v>
+        <v>-0.1400918276212835</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5179629290855559</v>
+        <v>-0.5478003702691581</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7679810024325278</v>
+        <v>-0.7900600343707183</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.088599231654641</v>
+        <v>-1.103968807993063</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.104264473090637</v>
+        <v>-1.099123595374408</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.427238559566888</v>
+        <v>-1.434677312654955</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.259117249319779</v>
+        <v>-1.281523066992499</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.277366610276424</v>
+        <v>-1.313315118593792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.03399</t>
+          <t>X &lt; 0.03407</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2926</v>
+        <v>2937</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8295711207624734</v>
+        <v>-0.8490948757344441</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4817479001649403</v>
+        <v>-0.515805017197799</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2449655015389069</v>
+        <v>-0.2468640761051688</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1303361629925419</v>
+        <v>-0.1325076348829413</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.002336485879652628</v>
+        <v>-0.02629695396715448</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.09551750350514254</v>
+        <v>-0.108411233095886</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6392855064476279</v>
+        <v>-0.660077785892625</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.9172609800155769</v>
+        <v>-0.9376760288506745</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.148891600702179</v>
+        <v>-1.160181466233553</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.077308690547383</v>
+        <v>-1.081603761270976</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.297379280301747</v>
+        <v>-1.301091388141238</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.517452095937522</v>
+        <v>-1.530483702978373</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.303946265016521</v>
+        <v>-1.328440681099032</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.264353208283374</v>
+        <v>-1.298948564240469</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.04526</t>
+          <t>X &lt; 0.04532</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3151</v>
+        <v>3162</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.058665714478721</v>
+        <v>-1.045544895753125</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8831233060199395</v>
+        <v>-0.8796783240314952</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8815604153740964</v>
+        <v>-0.8784545693313817</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6711058149388549</v>
+        <v>-0.6686182669789247</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4012670317845988</v>
+        <v>-0.4156130640045816</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5298209315936191</v>
+        <v>-0.5357515896859439</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.009063354521402</v>
+        <v>-1.021135399047225</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.332428098753823</v>
+        <v>-1.343782197571528</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.408043678979858</v>
+        <v>-1.426932162839897</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.480212148409933</v>
+        <v>-1.507327346379071</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.604196746208579</v>
+        <v>-1.6310717215068</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.83792492171365</v>
+        <v>-1.871724843419763</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.542849683044714</v>
+        <v>-1.585809375931881</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.680456505677498</v>
+        <v>-1.730529150608596</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.05653</t>
+          <t>X &lt; 0.05657</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3317</v>
+        <v>3328</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7091442587625849</v>
+        <v>-0.6992767455694064</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.892943217019635</v>
+        <v>-0.8896960956715745</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.18158504681476</v>
+        <v>-1.177652834266496</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.065394983340148</v>
+        <v>-1.061756398185402</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8059421271209288</v>
+        <v>-0.8158256211094681</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7329022340901261</v>
+        <v>-0.7366760236403636</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.252671359404985</v>
+        <v>-1.260949225172979</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.432821675509487</v>
+        <v>-1.440827182513928</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.537838593857749</v>
+        <v>-1.551709402167866</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.528476304233386</v>
+        <v>-1.549131812954087</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.536029339740601</v>
+        <v>-1.556811208341898</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.726198064257034</v>
+        <v>-1.752515874653284</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.527149288641631</v>
+        <v>-1.560604304565146</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.55612465185655</v>
+        <v>-1.595531370479165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0678</t>
+          <t>X &lt; 0.06782</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3457</v>
+        <v>3468</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9247200651164817</v>
+        <v>-0.9157423908163125</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9932263668959536</v>
+        <v>-0.9898406341807728</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.228511339956455</v>
+        <v>-1.224595165100851</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.169454825682081</v>
+        <v>-1.165653495440736</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7979961982990957</v>
+        <v>-0.8055521936656689</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9467702374318137</v>
+        <v>-0.9487503227741314</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.189202653958141</v>
+        <v>-1.195413647637999</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.352057300749927</v>
+        <v>-1.358011275919779</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.397500091128705</v>
+        <v>-1.40830318132695</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.27838888891575</v>
+        <v>-1.294997901324912</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.35165020470334</v>
+        <v>-1.368148461618851</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.417036928093118</v>
+        <v>-1.438282332754028</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.445396708554604</v>
+        <v>-1.471760066785066</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.406179623270276</v>
+        <v>-1.43752769955379</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3593</v>
+        <v>3604</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8724856367462266</v>
+        <v>-0.8651021483594761</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7772616242916683</v>
+        <v>-0.7747048392463753</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.157239768064649</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.12323176748481</v>
+        <v>-1.119732785200412</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8416341977050834</v>
+        <v>-0.8469455546959423</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8624902975562065</v>
+        <v>-0.8637504438384198</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.098940914158298</v>
+        <v>-1.103384695335983</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.245480707338388</v>
+        <v>-1.249679816419281</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.347067682598258</v>
+        <v>-1.354856799201841</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.236779846355084</v>
+        <v>-1.249144855865261</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.315000619743813</v>
+        <v>-1.327221607348406</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.320970188005276</v>
+        <v>-1.337042164670422</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.336304792943054</v>
+        <v>-1.356397087610297</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.289997360665197</v>
+        <v>-1.314026578794717</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.09034</t>
+          <t>X &lt; 0.09033</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3689</v>
+        <v>3700</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6710835075737904</v>
+        <v>-0.6652424470254132</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5119886407557104</v>
+        <v>-0.5103147721117978</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9463329678126797</v>
+        <v>-0.943507631313615</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.990873831107109</v>
+        <v>-0.9878706199461007</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.649399789142322</v>
+        <v>-0.6538872798418822</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8242341614199447</v>
+        <v>-0.8249549150903093</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.002620567837951</v>
+        <v>-1.005991729547986</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.076271172739801</v>
+        <v>-1.079588043401657</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.149686173951665</v>
+        <v>-1.155961325335895</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.064305582555058</v>
+        <v>-1.074287447562142</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.037426042477875</v>
+        <v>-1.047564646631777</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.150642710236369</v>
+        <v>-1.163596323010871</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-1.111593138008637</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.017012413654065</v>
+        <v>-1.036767077339874</v>
       </c>
     </row>
     <row r="28">
@@ -5052,101 +5052,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3781</v>
+        <v>3792</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2668938903129501</v>
+        <v>-0.2630684608922422</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1769953479588509</v>
+        <v>-0.1763593621984612</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5311773058215792</v>
+        <v>-0.5296248473451826</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7032587578009952</v>
+        <v>-0.7011723153227649</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5413759125835043</v>
+        <v>-0.5448923927277676</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5727552315878341</v>
+        <v>-0.5736064792758526</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7751992738907916</v>
+        <v>-0.7779846006150208</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.8319412540985454</v>
+        <v>-0.8346924852827584</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.878576500521703</v>
+        <v>-0.883710023878713</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8686982694942813</v>
+        <v>-0.8765972564549855</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9266786176131916</v>
+        <v>-0.9344704314581662</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9305404159888226</v>
+        <v>-0.9408185684910322</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9130127853165035</v>
+        <v>-0.925966990266943</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9370159066006707</v>
+        <v>-0.9523503821636936</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1129</t>
+          <t>X &lt; 0.1128</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3849</v>
+        <v>3860</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.09873063436656082</v>
+        <v>-0.09596258657042966</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.01284804434410347</v>
+        <v>-0.01271039764614557</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3158890523946738</v>
+        <v>-0.314978332095599</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4825877272940104</v>
+        <v>-0.4811738648948065</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3589088872747581</v>
+        <v>-0.3620291136285019</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4362986561798365</v>
+        <v>-0.4371018257081118</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5069630441721387</v>
+        <v>-0.5096181412967624</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5449330339502296</v>
+        <v>-0.5475862755996062</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5398528111638896</v>
+        <v>-0.5445711721741091</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5450608698252779</v>
+        <v>-0.5519938273250489</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6834289068564132</v>
+        <v>-0.6900175514100582</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7644541520353556</v>
+        <v>-0.772846407153672</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.702665755297339</v>
+        <v>-0.713372366915678</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7481828845075356</v>
+        <v>-0.7607553142814822</v>
       </c>
     </row>
     <row r="30">
@@ -5156,309 +5156,309 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3913</v>
+        <v>3924</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01526328683701905</v>
+        <v>0.01719322972312654</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.07936327009499422</v>
+        <v>-0.07906126776641287</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.180043742807861</v>
+        <v>-0.1795300749776203</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3418637611451771</v>
+        <v>-0.3408744280630458</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.177956785785085</v>
+        <v>-0.1807423667700974</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3001907691231978</v>
+        <v>-0.3009716878211179</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3710497576957152</v>
+        <v>-0.3732602790075461</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3649591199081215</v>
+        <v>-0.3672709014037352</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3864353081380614</v>
+        <v>-0.390313038555945</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4309357001432659</v>
+        <v>-0.4364566003028258</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5448224283360474</v>
+        <v>-0.5500637043404382</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5983829419899038</v>
+        <v>-0.6050872437809431</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5955311933850567</v>
+        <v>-0.6039389835969402</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6365844042599917</v>
+        <v>-0.6464593384082775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1354</t>
+          <t>X &lt; 0.1353</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3948</v>
+        <v>3959</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.08156819062191545</v>
+        <v>0.08304023956416984</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.001193032689094764</v>
+        <v>-0.001120690450797213</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.10445370537267</v>
+        <v>-0.1041553618336195</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2636721141332288</v>
+        <v>-0.2629125724363846</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1059563661799814</v>
+        <v>-0.1084887722883323</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1233475080434587</v>
+        <v>-0.124400530195949</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1942843612716558</v>
+        <v>-0.1965419431861335</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.217628172006755</v>
+        <v>-0.2198935634369903</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2141196341912348</v>
+        <v>-0.2177944768710987</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2404057874508467</v>
+        <v>-0.2455293727349996</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.355048773588365</v>
+        <v>-0.3598880516829723</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4330984956054991</v>
+        <v>-0.4391095625092802</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4592768322426721</v>
+        <v>-0.4666746202179226</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4472718200933699</v>
+        <v>-0.4560648798152442</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1467</t>
+          <t>X &lt; 0.1466</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3990</v>
+        <v>4000</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1046447988436086</v>
+        <v>0.09392505525256212</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1057989258770817</v>
+        <v>0.09414877689633983</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.04949240016964751</v>
+        <v>0.03802919737918131</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.05664836476485391</v>
+        <v>-0.06786604916281647</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.06880301737325567</v>
+        <v>0.05507969060563767</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05476227485608121</v>
+        <v>0.04216198379800318</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.01627474786691607</v>
+        <v>-0.02982034239698805</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.06926281119828559</v>
+        <v>-0.08262153956862761</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1164577136334373</v>
+        <v>-0.1308257407680244</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1013054365195956</v>
+        <v>-0.1167406746805923</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2419046818302206</v>
+        <v>-0.2319867540317873</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2936931025408924</v>
+        <v>-0.3097687797322664</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3239825492525696</v>
+        <v>-0.3410683955114777</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2846311759297748</v>
+        <v>-0.302983293556089</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.158</t>
+          <t>X &lt; 0.1578</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4027</v>
+        <v>4038</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.06858891996069616</v>
+        <v>0.06949814795922293</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.0549639818734704</v>
+        <v>0.05485923810530835</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.04507299981914059</v>
+        <v>0.04495630737226719</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03413164442797267</v>
+        <v>-0.03402032749859529</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.08524047658939793</v>
+        <v>0.08318546669395488</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.09884255539287068</v>
+        <v>0.09767379754076444</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.04667682557790442</v>
+        <v>-0.0483540394531019</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.02908501872692426</v>
+        <v>-0.03085695104093844</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.07639647637257951</v>
+        <v>-0.07894278343327699</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.09398237055125236</v>
+        <v>-0.09746257524415824</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1855405358899631</v>
+        <v>-0.1887934622893823</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2365236631408649</v>
+        <v>-0.2405335953442602</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2703800668051031</v>
+        <v>-0.275239346460296</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2541352689161442</v>
+        <v>-0.2599174193609457</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1692</t>
+          <t>X &lt; 0.1691</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4058</v>
+        <v>4069</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03689286162973104</v>
+        <v>0.03765887574996185</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1339421024460421</v>
+        <v>0.1336162602585631</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.04741009941281504</v>
+        <v>0.04728682713265187</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.005615916387277764</v>
+        <v>-0.005586103036463896</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1333384529287258</v>
+        <v>0.1315383599238515</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1491158953456093</v>
+        <v>0.1480025469689394</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07787335398437989</v>
+        <v>0.07623792217582803</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.01797994336730113</v>
+        <v>0.01646908829325611</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.01980047521140449</v>
+        <v>0.0175712372362824</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.004113858902059064</v>
+        <v>-0.007054142209874215</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.09651358155888801</v>
+        <v>-0.09922164220750318</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1468230076713439</v>
+        <v>-0.1501028499852808</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1343343576976537</v>
+        <v>-0.1383917919350992</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1164556854539569</v>
+        <v>-0.1212555963331923</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.1805</t>
+          <t>X &lt; 0.1803</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1198165701982532</v>
+        <v>0.1201853012698635</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.109168027842955</v>
+        <v>0.1089035381910293</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.04525451510145473</v>
+        <v>0.04513684433251086</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.09105447003474865</v>
+        <v>0.09082204658611204</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1282837883237562</v>
+        <v>0.1267918146794713</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1212625176425064</v>
+        <v>0.1203705994854261</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.09884583076710385</v>
+        <v>0.09744474857185992</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.06102892868248233</v>
+        <v>0.05969974308411707</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.06249119883452181</v>
+        <v>0.06058945582920927</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.0337355978660554</v>
+        <v>0.03129288804665009</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.05931464743404291</v>
+        <v>-0.06152134137252574</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06014569430620043</v>
+        <v>-0.0629141850515893</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.05017888385381752</v>
+        <v>-0.05356699289436762</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.03105750633196891</v>
+        <v>-0.03505023711826993</v>
       </c>
     </row>
   </sheetData>
